--- a/PT_HGSS_move_tutor_hex_creator.xlsx
+++ b/PT_HGSS_move_tutor_hex_creator.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21780" windowHeight="11835" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18660" windowHeight="7050"/>
   </bookViews>
   <sheets>
     <sheet name="HGSS" sheetId="5" r:id="rId1"/>
@@ -4374,15 +4374,26 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -4396,12 +4407,6 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4414,15 +4419,16 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4441,78 +4447,27 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4522,33 +4477,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4580,6 +4508,78 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5222,48 +5222,48 @@
   <sheetData>
     <row r="1" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="126" t="s">
+      <c r="B2" s="129" t="s">
         <v>984</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="130" t="s">
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="137" t="s">
         <v>570</v>
       </c>
-      <c r="K2" s="132" t="s">
+      <c r="K2" s="133" t="s">
         <v>1000</v>
       </c>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="133"/>
+      <c r="Q2" s="133"/>
+      <c r="R2" s="134"/>
     </row>
     <row r="3" spans="2:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="128"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="131"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="134"/>
-      <c r="M3" s="134"/>
-      <c r="N3" s="134"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="Q3" s="134"/>
-      <c r="R3" s="135"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="132"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="135"/>
+      <c r="O3" s="135"/>
+      <c r="P3" s="135"/>
+      <c r="Q3" s="135"/>
+      <c r="R3" s="136"/>
     </row>
     <row r="4" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="38"/>
@@ -5312,11 +5312,11 @@
     <row r="6" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="38"/>
       <c r="C6" s="39"/>
-      <c r="D6" s="144" t="str">
+      <c r="D6" s="125" t="str">
         <f>VLOOKUP(E5,Lookups!A:B,2,0)</f>
         <v>Bulbasaur</v>
       </c>
-      <c r="E6" s="145"/>
+      <c r="E6" s="126"/>
       <c r="F6" s="25"/>
       <c r="G6" s="39"/>
       <c r="H6" s="14" t="s">
@@ -5331,14 +5331,14 @@
       <c r="L6" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="M6" s="146" t="str">
+      <c r="M6" s="127" t="str">
         <f>IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(E16&amp;E15&amp;E14&amp;E13&amp;E12&amp;E11&amp;E10&amp;E9,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(E16&amp;E15&amp;E14&amp;E13&amp;E12&amp;E11&amp;E10&amp;E9,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(E16&amp;E15&amp;E14&amp;E13&amp;E12&amp;E11&amp;E10&amp;E9,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(E24&amp;E23&amp;E22&amp;E21&amp;E20&amp;E19&amp;E18&amp;E17,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(E24&amp;E23&amp;E22&amp;E21&amp;E20&amp;E19&amp;E18&amp;E17,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(E24&amp;E23&amp;E22&amp;E21&amp;E20&amp;E19&amp;E18&amp;E17,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(I16&amp;I15&amp;I14&amp;I13&amp;I12&amp;I11&amp;I10&amp;I9,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(I16&amp;I15&amp;I14&amp;I13&amp;I12&amp;I11&amp;I10&amp;I9,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(I16&amp;I15&amp;I14&amp;I13&amp;I12&amp;I11&amp;I10&amp;I9,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(I24&amp;I23&amp;I22&amp;I21&amp;I20&amp;I19&amp;I18&amp;I17,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(I24&amp;I23&amp;I22&amp;I21&amp;I20&amp;I19&amp;I18&amp;I17,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(I24&amp;I23&amp;I22&amp;I21&amp;I20&amp;I19&amp;I18&amp;I17,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(M16&amp;M15&amp;M14&amp;M13&amp;M12&amp;M11&amp;M10&amp;M9,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(M16&amp;M15&amp;M14&amp;M13&amp;M12&amp;M11&amp;M10&amp;M9,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(M16&amp;M15&amp;M14&amp;M13&amp;M12&amp;M11&amp;M10&amp;M9,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(M24&amp;M23&amp;M22&amp;M21&amp;M20&amp;M19&amp;M18&amp;M17,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(M24&amp;M23&amp;M22&amp;M21&amp;M20&amp;M19&amp;M18&amp;M17,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(M24&amp;M23&amp;M22&amp;M21&amp;M20&amp;M19&amp;M18&amp;M17,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(Q16&amp;Q15&amp;Q14&amp;Q13&amp;Q12&amp;Q11&amp;Q10&amp;Q9,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(Q16&amp;Q15&amp;Q14&amp;Q13&amp;Q12&amp;Q11&amp;Q10&amp;Q9,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(Q16&amp;Q15&amp;Q14&amp;Q13&amp;Q12&amp;Q11&amp;Q10&amp;Q9,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(Q24&amp;Q23&amp;Q22&amp;Q21&amp;Q20&amp;Q19&amp;Q18&amp;Q17,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(Q24&amp;Q23&amp;Q22&amp;Q21&amp;Q20&amp;Q19&amp;Q18&amp;Q17,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(Q24&amp;Q23&amp;Q22&amp;Q21&amp;Q20&amp;Q19&amp;Q18&amp;Q17,"N",0),"Y",1)))</f>
         <v>00 00 00 00 00 00 00 00</v>
       </c>
-      <c r="N6" s="146"/>
-      <c r="O6" s="146"/>
-      <c r="P6" s="146"/>
-      <c r="Q6" s="147"/>
+      <c r="N6" s="127"/>
+      <c r="O6" s="127"/>
+      <c r="P6" s="127"/>
+      <c r="Q6" s="128"/>
       <c r="R6" s="40"/>
     </row>
     <row r="7" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6160,29 +6160,29 @@
     </row>
     <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="51"/>
-      <c r="B27" s="126" t="s">
+      <c r="B27" s="129" t="s">
         <v>984</v>
       </c>
-      <c r="C27" s="127"/>
-      <c r="D27" s="127"/>
-      <c r="E27" s="127"/>
-      <c r="F27" s="127"/>
-      <c r="G27" s="127"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="127"/>
-      <c r="J27" s="130" t="s">
+      <c r="C27" s="130"/>
+      <c r="D27" s="130"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="130"/>
+      <c r="G27" s="130"/>
+      <c r="H27" s="130"/>
+      <c r="I27" s="130"/>
+      <c r="J27" s="137" t="s">
         <v>570</v>
       </c>
-      <c r="K27" s="132" t="s">
+      <c r="K27" s="133" t="s">
         <v>999</v>
       </c>
-      <c r="L27" s="132"/>
-      <c r="M27" s="132"/>
-      <c r="N27" s="132"/>
-      <c r="O27" s="132"/>
-      <c r="P27" s="132"/>
-      <c r="Q27" s="132"/>
-      <c r="R27" s="133"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="133"/>
+      <c r="N27" s="133"/>
+      <c r="O27" s="133"/>
+      <c r="P27" s="133"/>
+      <c r="Q27" s="133"/>
+      <c r="R27" s="134"/>
       <c r="S27" s="51"/>
       <c r="T27" s="51"/>
       <c r="U27" s="51"/>
@@ -6196,23 +6196,23 @@
     </row>
     <row r="28" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="51"/>
-      <c r="B28" s="128"/>
-      <c r="C28" s="129"/>
-      <c r="D28" s="129"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="129"/>
-      <c r="G28" s="129"/>
-      <c r="H28" s="129"/>
-      <c r="I28" s="129"/>
-      <c r="J28" s="131"/>
-      <c r="K28" s="134"/>
-      <c r="L28" s="134"/>
-      <c r="M28" s="134"/>
-      <c r="N28" s="134"/>
-      <c r="O28" s="134"/>
-      <c r="P28" s="134"/>
-      <c r="Q28" s="134"/>
-      <c r="R28" s="135"/>
+      <c r="B28" s="131"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="132"/>
+      <c r="J28" s="138"/>
+      <c r="K28" s="135"/>
+      <c r="L28" s="135"/>
+      <c r="M28" s="135"/>
+      <c r="N28" s="135"/>
+      <c r="O28" s="135"/>
+      <c r="P28" s="135"/>
+      <c r="Q28" s="135"/>
+      <c r="R28" s="136"/>
       <c r="S28" s="51"/>
       <c r="T28" s="51"/>
       <c r="U28" s="51"/>
@@ -6294,30 +6294,30 @@
       <c r="E31" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="138" t="s">
+      <c r="F31" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="G31" s="138"/>
+      <c r="G31" s="139"/>
       <c r="H31" s="58" t="s">
         <v>3</v>
       </c>
       <c r="I31" s="58" t="s">
         <v>989</v>
       </c>
-      <c r="J31" s="138" t="s">
+      <c r="J31" s="139" t="s">
         <v>990</v>
       </c>
-      <c r="K31" s="138"/>
+      <c r="K31" s="139"/>
       <c r="L31" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="M31" s="138" t="s">
+      <c r="M31" s="139" t="s">
         <v>991</v>
       </c>
-      <c r="N31" s="138"/>
-      <c r="O31" s="138"/>
-      <c r="P31" s="138"/>
-      <c r="Q31" s="148"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="139"/>
+      <c r="P31" s="139"/>
+      <c r="Q31" s="140"/>
       <c r="R31" s="73"/>
       <c r="S31" s="51"/>
       <c r="T31" s="51"/>
@@ -6338,10 +6338,10 @@
       <c r="E32" s="59">
         <v>1</v>
       </c>
-      <c r="F32" s="136">
+      <c r="F32" s="124">
         <v>291</v>
       </c>
-      <c r="G32" s="136"/>
+      <c r="G32" s="124"/>
       <c r="H32" s="53" t="str">
         <f>VLOOKUP(F32,Lookups!$D:$E,2,0)</f>
         <v>Dive</v>
@@ -6349,22 +6349,22 @@
       <c r="I32" s="110">
         <v>40</v>
       </c>
-      <c r="J32" s="136">
+      <c r="J32" s="124">
         <v>0</v>
       </c>
-      <c r="K32" s="136"/>
+      <c r="K32" s="124"/>
       <c r="L32" s="117" t="str">
         <f>DEC2HEX(146144+((E32-1)*4))</f>
         <v>23AE0</v>
       </c>
-      <c r="M32" s="139" t="str">
+      <c r="M32" s="141" t="str">
         <f>IF(LEN(DEC2HEX(F32))=1,"0"&amp;DEC2HEX(F32)&amp;" 00",IF(LEN(DEC2HEX(F32))=2,DEC2HEX(F32)&amp;" 00",IF(LEN(DEC2HEX(F32))=3,RIGHT(DEC2HEX(F32),2)&amp;" 0"&amp;LEFT(DEC2HEX(F32),1),IF(LEN(DEC2HEX(F32))=4,RIGHT(DEC2HEX(F32),2)&amp;" "&amp;LEFT(DEC2HEX(F32),2),"Error - Move ID too high"))))&amp;" "&amp;IF(LEN(DEC2HEX(I32))=1,"0"&amp;DEC2HEX(I32),DEC2HEX(I32))&amp;" "&amp;IF(LEN(DEC2HEX(J32))=1,"0"&amp;DEC2HEX(J32),DEC2HEX(J32))</f>
         <v>23 01 28 00</v>
       </c>
-      <c r="N32" s="139"/>
-      <c r="O32" s="139"/>
-      <c r="P32" s="139"/>
-      <c r="Q32" s="140"/>
+      <c r="N32" s="141"/>
+      <c r="O32" s="141"/>
+      <c r="P32" s="141"/>
+      <c r="Q32" s="142"/>
       <c r="R32" s="70"/>
       <c r="S32" s="51"/>
       <c r="T32" s="51"/>
@@ -6385,10 +6385,10 @@
       <c r="E33" s="59">
         <v>2</v>
       </c>
-      <c r="F33" s="136">
+      <c r="F33" s="124">
         <v>189</v>
       </c>
-      <c r="G33" s="136"/>
+      <c r="G33" s="124"/>
       <c r="H33" s="53" t="str">
         <f>VLOOKUP(F33,Lookups!$D:$E,2,0)</f>
         <v>Mud-Slap</v>
@@ -6396,22 +6396,22 @@
       <c r="I33" s="110">
         <v>32</v>
       </c>
-      <c r="J33" s="136">
+      <c r="J33" s="124">
         <v>1</v>
       </c>
-      <c r="K33" s="136"/>
+      <c r="K33" s="124"/>
       <c r="L33" s="117" t="str">
         <f t="shared" ref="L33:L89" si="4">DEC2HEX(146144+((E33-1)*4))</f>
         <v>23AE4</v>
       </c>
-      <c r="M33" s="139" t="str">
+      <c r="M33" s="141" t="str">
         <f t="shared" ref="M33:M89" si="5">IF(LEN(DEC2HEX(F33))=1,"0"&amp;DEC2HEX(F33)&amp;" 00",IF(LEN(DEC2HEX(F33))=2,DEC2HEX(F33)&amp;" 00",IF(LEN(DEC2HEX(F33))=3,RIGHT(DEC2HEX(F33),2)&amp;" 0"&amp;LEFT(DEC2HEX(F33),1),IF(LEN(DEC2HEX(F33))=4,RIGHT(DEC2HEX(F33),2)&amp;" "&amp;LEFT(DEC2HEX(F33),2),"Error - Move ID too high"))))&amp;" "&amp;IF(LEN(DEC2HEX(I33))=1,"0"&amp;DEC2HEX(I33),DEC2HEX(I33))&amp;" "&amp;IF(LEN(DEC2HEX(J33))=1,"0"&amp;DEC2HEX(J33),DEC2HEX(J33))</f>
         <v>BD 00 20 01</v>
       </c>
-      <c r="N33" s="139"/>
-      <c r="O33" s="139"/>
-      <c r="P33" s="139"/>
-      <c r="Q33" s="140"/>
+      <c r="N33" s="141"/>
+      <c r="O33" s="141"/>
+      <c r="P33" s="141"/>
+      <c r="Q33" s="142"/>
       <c r="R33" s="70"/>
       <c r="S33" s="51"/>
       <c r="T33" s="51"/>
@@ -6432,10 +6432,10 @@
       <c r="E34" s="59">
         <v>3</v>
       </c>
-      <c r="F34" s="136">
+      <c r="F34" s="124">
         <v>210</v>
       </c>
-      <c r="G34" s="136"/>
+      <c r="G34" s="124"/>
       <c r="H34" s="53" t="str">
         <f>VLOOKUP(F34,Lookups!$D:$E,2,0)</f>
         <v>Fury Cutter</v>
@@ -6443,22 +6443,22 @@
       <c r="I34" s="110">
         <v>32</v>
       </c>
-      <c r="J34" s="136">
+      <c r="J34" s="124">
         <v>0</v>
       </c>
-      <c r="K34" s="136"/>
+      <c r="K34" s="124"/>
       <c r="L34" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23AE8</v>
       </c>
-      <c r="M34" s="139" t="str">
+      <c r="M34" s="141" t="str">
         <f t="shared" si="5"/>
         <v>D2 00 20 00</v>
       </c>
-      <c r="N34" s="139"/>
-      <c r="O34" s="139"/>
-      <c r="P34" s="139"/>
-      <c r="Q34" s="140"/>
+      <c r="N34" s="141"/>
+      <c r="O34" s="141"/>
+      <c r="P34" s="141"/>
+      <c r="Q34" s="142"/>
       <c r="R34" s="70"/>
       <c r="S34" s="51"/>
       <c r="T34" s="51"/>
@@ -6479,10 +6479,10 @@
       <c r="E35" s="59">
         <v>4</v>
       </c>
-      <c r="F35" s="136">
+      <c r="F35" s="124">
         <v>196</v>
       </c>
-      <c r="G35" s="136"/>
+      <c r="G35" s="124"/>
       <c r="H35" s="53" t="str">
         <f>VLOOKUP(F35,Lookups!$D:$E,2,0)</f>
         <v>Icy Wind</v>
@@ -6490,22 +6490,22 @@
       <c r="I35" s="110">
         <v>48</v>
       </c>
-      <c r="J35" s="136">
+      <c r="J35" s="124">
         <v>0</v>
       </c>
-      <c r="K35" s="136"/>
+      <c r="K35" s="124"/>
       <c r="L35" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23AEC</v>
       </c>
-      <c r="M35" s="139" t="str">
+      <c r="M35" s="141" t="str">
         <f t="shared" si="5"/>
         <v>C4 00 30 00</v>
       </c>
-      <c r="N35" s="139"/>
-      <c r="O35" s="139"/>
-      <c r="P35" s="139"/>
-      <c r="Q35" s="140"/>
+      <c r="N35" s="141"/>
+      <c r="O35" s="141"/>
+      <c r="P35" s="141"/>
+      <c r="Q35" s="142"/>
       <c r="R35" s="70"/>
       <c r="S35" s="51"/>
       <c r="T35" s="51"/>
@@ -6526,10 +6526,10 @@
       <c r="E36" s="59">
         <v>5</v>
       </c>
-      <c r="F36" s="136">
+      <c r="F36" s="124">
         <v>205</v>
       </c>
-      <c r="G36" s="136"/>
+      <c r="G36" s="124"/>
       <c r="H36" s="53" t="str">
         <f>VLOOKUP(F36,Lookups!$D:$E,2,0)</f>
         <v>Rollout</v>
@@ -6537,22 +6537,22 @@
       <c r="I36" s="110">
         <v>32</v>
       </c>
-      <c r="J36" s="136">
+      <c r="J36" s="124">
         <v>1</v>
       </c>
-      <c r="K36" s="136"/>
+      <c r="K36" s="124"/>
       <c r="L36" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23AF0</v>
       </c>
-      <c r="M36" s="139" t="str">
+      <c r="M36" s="141" t="str">
         <f t="shared" si="5"/>
         <v>CD 00 20 01</v>
       </c>
-      <c r="N36" s="139"/>
-      <c r="O36" s="139"/>
-      <c r="P36" s="139"/>
-      <c r="Q36" s="140"/>
+      <c r="N36" s="141"/>
+      <c r="O36" s="141"/>
+      <c r="P36" s="141"/>
+      <c r="Q36" s="142"/>
       <c r="R36" s="70"/>
       <c r="S36" s="51"/>
       <c r="T36" s="51"/>
@@ -6573,10 +6573,10 @@
       <c r="E37" s="59">
         <v>6</v>
       </c>
-      <c r="F37" s="136">
+      <c r="F37" s="124">
         <v>9</v>
       </c>
-      <c r="G37" s="136"/>
+      <c r="G37" s="124"/>
       <c r="H37" s="53" t="str">
         <f>VLOOKUP(F37,Lookups!$D:$E,2,0)</f>
         <v>ThunderPunch</v>
@@ -6584,22 +6584,22 @@
       <c r="I37" s="110">
         <v>64</v>
       </c>
-      <c r="J37" s="136">
+      <c r="J37" s="124">
         <v>0</v>
       </c>
-      <c r="K37" s="136"/>
+      <c r="K37" s="124"/>
       <c r="L37" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23AF4</v>
       </c>
-      <c r="M37" s="139" t="str">
+      <c r="M37" s="141" t="str">
         <f t="shared" si="5"/>
         <v>09 00 40 00</v>
       </c>
-      <c r="N37" s="139"/>
-      <c r="O37" s="139"/>
-      <c r="P37" s="139"/>
-      <c r="Q37" s="140"/>
+      <c r="N37" s="141"/>
+      <c r="O37" s="141"/>
+      <c r="P37" s="141"/>
+      <c r="Q37" s="142"/>
       <c r="R37" s="70"/>
       <c r="S37" s="51"/>
       <c r="T37" s="51"/>
@@ -6620,10 +6620,10 @@
       <c r="E38" s="59">
         <v>7</v>
       </c>
-      <c r="F38" s="136">
+      <c r="F38" s="124">
         <v>7</v>
       </c>
-      <c r="G38" s="136"/>
+      <c r="G38" s="124"/>
       <c r="H38" s="53" t="str">
         <f>VLOOKUP(F38,Lookups!$D:$E,2,0)</f>
         <v>Fire Punch</v>
@@ -6631,22 +6631,22 @@
       <c r="I38" s="110">
         <v>64</v>
       </c>
-      <c r="J38" s="136">
+      <c r="J38" s="124">
         <v>0</v>
       </c>
-      <c r="K38" s="136"/>
+      <c r="K38" s="124"/>
       <c r="L38" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23AF8</v>
       </c>
-      <c r="M38" s="139" t="str">
+      <c r="M38" s="141" t="str">
         <f t="shared" si="5"/>
         <v>07 00 40 00</v>
       </c>
-      <c r="N38" s="139"/>
-      <c r="O38" s="139"/>
-      <c r="P38" s="139"/>
-      <c r="Q38" s="140"/>
+      <c r="N38" s="141"/>
+      <c r="O38" s="141"/>
+      <c r="P38" s="141"/>
+      <c r="Q38" s="142"/>
       <c r="R38" s="70"/>
       <c r="S38" s="51"/>
       <c r="T38" s="51"/>
@@ -6667,10 +6667,10 @@
       <c r="E39" s="59">
         <v>8</v>
       </c>
-      <c r="F39" s="136">
+      <c r="F39" s="124">
         <v>276</v>
       </c>
-      <c r="G39" s="136"/>
+      <c r="G39" s="124"/>
       <c r="H39" s="53" t="str">
         <f>VLOOKUP(F39,Lookups!$D:$E,2,0)</f>
         <v>Superpower</v>
@@ -6678,22 +6678,22 @@
       <c r="I39" s="110">
         <v>48</v>
       </c>
-      <c r="J39" s="136">
+      <c r="J39" s="124">
         <v>1</v>
       </c>
-      <c r="K39" s="136"/>
+      <c r="K39" s="124"/>
       <c r="L39" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23AFC</v>
       </c>
-      <c r="M39" s="139" t="str">
+      <c r="M39" s="141" t="str">
         <f t="shared" si="5"/>
         <v>14 01 30 01</v>
       </c>
-      <c r="N39" s="139"/>
-      <c r="O39" s="139"/>
-      <c r="P39" s="139"/>
-      <c r="Q39" s="140"/>
+      <c r="N39" s="141"/>
+      <c r="O39" s="141"/>
+      <c r="P39" s="141"/>
+      <c r="Q39" s="142"/>
       <c r="R39" s="70"/>
       <c r="S39" s="51"/>
       <c r="T39" s="51"/>
@@ -6714,10 +6714,10 @@
       <c r="E40" s="59">
         <v>9</v>
       </c>
-      <c r="F40" s="136">
+      <c r="F40" s="124">
         <v>8</v>
       </c>
-      <c r="G40" s="136"/>
+      <c r="G40" s="124"/>
       <c r="H40" s="53" t="str">
         <f>VLOOKUP(F40,Lookups!$D:$E,2,0)</f>
         <v>Ice Punch</v>
@@ -6725,22 +6725,22 @@
       <c r="I40" s="110">
         <v>64</v>
       </c>
-      <c r="J40" s="136">
+      <c r="J40" s="124">
         <v>0</v>
       </c>
-      <c r="K40" s="136"/>
+      <c r="K40" s="124"/>
       <c r="L40" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B00</v>
       </c>
-      <c r="M40" s="139" t="str">
+      <c r="M40" s="141" t="str">
         <f t="shared" si="5"/>
         <v>08 00 40 00</v>
       </c>
-      <c r="N40" s="139"/>
-      <c r="O40" s="139"/>
-      <c r="P40" s="139"/>
-      <c r="Q40" s="140"/>
+      <c r="N40" s="141"/>
+      <c r="O40" s="141"/>
+      <c r="P40" s="141"/>
+      <c r="Q40" s="142"/>
       <c r="R40" s="70"/>
       <c r="S40" s="51"/>
       <c r="T40" s="51"/>
@@ -6761,10 +6761,10 @@
       <c r="E41" s="59">
         <v>10</v>
       </c>
-      <c r="F41" s="136">
+      <c r="F41" s="124">
         <v>442</v>
       </c>
-      <c r="G41" s="136"/>
+      <c r="G41" s="124"/>
       <c r="H41" s="53" t="str">
         <f>VLOOKUP(F41,Lookups!$D:$E,2,0)</f>
         <v>Iron Head</v>
@@ -6772,22 +6772,22 @@
       <c r="I41" s="110">
         <v>40</v>
       </c>
-      <c r="J41" s="136">
+      <c r="J41" s="124">
         <v>1</v>
       </c>
-      <c r="K41" s="136"/>
+      <c r="K41" s="124"/>
       <c r="L41" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B04</v>
       </c>
-      <c r="M41" s="139" t="str">
+      <c r="M41" s="141" t="str">
         <f t="shared" si="5"/>
         <v>BA 01 28 01</v>
       </c>
-      <c r="N41" s="139"/>
-      <c r="O41" s="139"/>
-      <c r="P41" s="139"/>
-      <c r="Q41" s="140"/>
+      <c r="N41" s="141"/>
+      <c r="O41" s="141"/>
+      <c r="P41" s="141"/>
+      <c r="Q41" s="142"/>
       <c r="R41" s="70"/>
       <c r="S41" s="51"/>
       <c r="T41" s="51"/>
@@ -6808,10 +6808,10 @@
       <c r="E42" s="59">
         <v>11</v>
       </c>
-      <c r="F42" s="136">
+      <c r="F42" s="124">
         <v>401</v>
       </c>
-      <c r="G42" s="136"/>
+      <c r="G42" s="124"/>
       <c r="H42" s="53" t="str">
         <f>VLOOKUP(F42,Lookups!$D:$E,2,0)</f>
         <v>Aqua Tail</v>
@@ -6819,22 +6819,22 @@
       <c r="I42" s="110">
         <v>40</v>
       </c>
-      <c r="J42" s="136">
+      <c r="J42" s="124">
         <v>1</v>
       </c>
-      <c r="K42" s="136"/>
+      <c r="K42" s="124"/>
       <c r="L42" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B08</v>
       </c>
-      <c r="M42" s="139" t="str">
+      <c r="M42" s="141" t="str">
         <f t="shared" si="5"/>
         <v>91 01 28 01</v>
       </c>
-      <c r="N42" s="139"/>
-      <c r="O42" s="139"/>
-      <c r="P42" s="139"/>
-      <c r="Q42" s="140"/>
+      <c r="N42" s="141"/>
+      <c r="O42" s="141"/>
+      <c r="P42" s="141"/>
+      <c r="Q42" s="142"/>
       <c r="R42" s="70"/>
       <c r="S42" s="51"/>
       <c r="T42" s="51"/>
@@ -6855,10 +6855,10 @@
       <c r="E43" s="59">
         <v>12</v>
       </c>
-      <c r="F43" s="136">
+      <c r="F43" s="124">
         <v>466</v>
       </c>
-      <c r="G43" s="136"/>
+      <c r="G43" s="124"/>
       <c r="H43" s="53" t="str">
         <f>VLOOKUP(F43,Lookups!$D:$E,2,0)</f>
         <v>Ominous Wind</v>
@@ -6866,22 +6866,22 @@
       <c r="I43" s="110">
         <v>48</v>
       </c>
-      <c r="J43" s="136">
+      <c r="J43" s="124">
         <v>0</v>
       </c>
-      <c r="K43" s="136"/>
+      <c r="K43" s="124"/>
       <c r="L43" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B0C</v>
       </c>
-      <c r="M43" s="139" t="str">
+      <c r="M43" s="141" t="str">
         <f t="shared" si="5"/>
         <v>D2 01 30 00</v>
       </c>
-      <c r="N43" s="139"/>
-      <c r="O43" s="139"/>
-      <c r="P43" s="139"/>
-      <c r="Q43" s="140"/>
+      <c r="N43" s="141"/>
+      <c r="O43" s="141"/>
+      <c r="P43" s="141"/>
+      <c r="Q43" s="142"/>
       <c r="R43" s="70"/>
       <c r="S43" s="51"/>
       <c r="T43" s="51"/>
@@ -6902,10 +6902,10 @@
       <c r="E44" s="59">
         <v>13</v>
       </c>
-      <c r="F44" s="136">
+      <c r="F44" s="124">
         <v>380</v>
       </c>
-      <c r="G44" s="136"/>
+      <c r="G44" s="124"/>
       <c r="H44" s="53" t="str">
         <f>VLOOKUP(F44,Lookups!$D:$E,2,0)</f>
         <v>Gastro Acid</v>
@@ -6913,22 +6913,22 @@
       <c r="I44" s="110">
         <v>32</v>
       </c>
-      <c r="J44" s="136">
+      <c r="J44" s="124">
         <v>1</v>
       </c>
-      <c r="K44" s="136"/>
+      <c r="K44" s="124"/>
       <c r="L44" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B10</v>
       </c>
-      <c r="M44" s="139" t="str">
+      <c r="M44" s="141" t="str">
         <f t="shared" si="5"/>
         <v>7C 01 20 01</v>
       </c>
-      <c r="N44" s="139"/>
-      <c r="O44" s="139"/>
-      <c r="P44" s="139"/>
-      <c r="Q44" s="140"/>
+      <c r="N44" s="141"/>
+      <c r="O44" s="141"/>
+      <c r="P44" s="141"/>
+      <c r="Q44" s="142"/>
       <c r="R44" s="70"/>
       <c r="S44" s="51"/>
       <c r="T44" s="51"/>
@@ -6949,10 +6949,10 @@
       <c r="E45" s="59">
         <v>14</v>
       </c>
-      <c r="F45" s="136">
+      <c r="F45" s="124">
         <v>173</v>
       </c>
-      <c r="G45" s="136"/>
+      <c r="G45" s="124"/>
       <c r="H45" s="53" t="str">
         <f>VLOOKUP(F45,Lookups!$D:$E,2,0)</f>
         <v>Snore</v>
@@ -6960,22 +6960,22 @@
       <c r="I45" s="110">
         <v>32</v>
       </c>
-      <c r="J45" s="136">
+      <c r="J45" s="124">
         <v>2</v>
       </c>
-      <c r="K45" s="136"/>
+      <c r="K45" s="124"/>
       <c r="L45" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B14</v>
       </c>
-      <c r="M45" s="139" t="str">
+      <c r="M45" s="141" t="str">
         <f t="shared" si="5"/>
         <v>AD 00 20 02</v>
       </c>
-      <c r="N45" s="139"/>
-      <c r="O45" s="139"/>
-      <c r="P45" s="139"/>
-      <c r="Q45" s="140"/>
+      <c r="N45" s="141"/>
+      <c r="O45" s="141"/>
+      <c r="P45" s="141"/>
+      <c r="Q45" s="142"/>
       <c r="R45" s="70"/>
       <c r="S45" s="51"/>
       <c r="T45" s="51"/>
@@ -6996,10 +6996,10 @@
       <c r="E46" s="59">
         <v>15</v>
       </c>
-      <c r="F46" s="136">
+      <c r="F46" s="124">
         <v>180</v>
       </c>
-      <c r="G46" s="136"/>
+      <c r="G46" s="124"/>
       <c r="H46" s="53" t="str">
         <f>VLOOKUP(F46,Lookups!$D:$E,2,0)</f>
         <v>Spite</v>
@@ -7007,22 +7007,22 @@
       <c r="I46" s="110">
         <v>40</v>
       </c>
-      <c r="J46" s="136">
+      <c r="J46" s="124">
         <v>2</v>
       </c>
-      <c r="K46" s="136"/>
+      <c r="K46" s="124"/>
       <c r="L46" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B18</v>
       </c>
-      <c r="M46" s="139" t="str">
+      <c r="M46" s="141" t="str">
         <f t="shared" si="5"/>
         <v>B4 00 28 02</v>
       </c>
-      <c r="N46" s="139"/>
-      <c r="O46" s="139"/>
-      <c r="P46" s="139"/>
-      <c r="Q46" s="140"/>
+      <c r="N46" s="141"/>
+      <c r="O46" s="141"/>
+      <c r="P46" s="141"/>
+      <c r="Q46" s="142"/>
       <c r="R46" s="70"/>
       <c r="S46" s="51"/>
       <c r="T46" s="51"/>
@@ -7043,10 +7043,10 @@
       <c r="E47" s="59">
         <v>16</v>
       </c>
-      <c r="F47" s="136">
+      <c r="F47" s="124">
         <v>314</v>
       </c>
-      <c r="G47" s="136"/>
+      <c r="G47" s="124"/>
       <c r="H47" s="53" t="str">
         <f>VLOOKUP(F47,Lookups!$D:$E,2,0)</f>
         <v>Air Cutter</v>
@@ -7054,22 +7054,22 @@
       <c r="I47" s="110">
         <v>48</v>
       </c>
-      <c r="J47" s="136">
+      <c r="J47" s="124">
         <v>0</v>
       </c>
-      <c r="K47" s="136"/>
+      <c r="K47" s="124"/>
       <c r="L47" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B1C</v>
       </c>
-      <c r="M47" s="139" t="str">
+      <c r="M47" s="141" t="str">
         <f t="shared" si="5"/>
         <v>3A 01 30 00</v>
       </c>
-      <c r="N47" s="139"/>
-      <c r="O47" s="139"/>
-      <c r="P47" s="139"/>
-      <c r="Q47" s="140"/>
+      <c r="N47" s="141"/>
+      <c r="O47" s="141"/>
+      <c r="P47" s="141"/>
+      <c r="Q47" s="142"/>
       <c r="R47" s="70"/>
       <c r="S47" s="51"/>
       <c r="T47" s="51"/>
@@ -7090,10 +7090,10 @@
       <c r="E48" s="59">
         <v>17</v>
       </c>
-      <c r="F48" s="136">
+      <c r="F48" s="124">
         <v>270</v>
       </c>
-      <c r="G48" s="136"/>
+      <c r="G48" s="124"/>
       <c r="H48" s="53" t="str">
         <f>VLOOKUP(F48,Lookups!$D:$E,2,0)</f>
         <v>Helping Hand</v>
@@ -7101,22 +7101,22 @@
       <c r="I48" s="110">
         <v>40</v>
       </c>
-      <c r="J48" s="136">
+      <c r="J48" s="124">
         <v>2</v>
       </c>
-      <c r="K48" s="136"/>
+      <c r="K48" s="124"/>
       <c r="L48" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B20</v>
       </c>
-      <c r="M48" s="139" t="str">
+      <c r="M48" s="141" t="str">
         <f t="shared" si="5"/>
         <v>0E 01 28 02</v>
       </c>
-      <c r="N48" s="139"/>
-      <c r="O48" s="139"/>
-      <c r="P48" s="139"/>
-      <c r="Q48" s="140"/>
+      <c r="N48" s="141"/>
+      <c r="O48" s="141"/>
+      <c r="P48" s="141"/>
+      <c r="Q48" s="142"/>
       <c r="R48" s="70"/>
       <c r="S48" s="51"/>
       <c r="T48" s="51"/>
@@ -7137,10 +7137,10 @@
       <c r="E49" s="59">
         <v>18</v>
       </c>
-      <c r="F49" s="136">
+      <c r="F49" s="124">
         <v>283</v>
       </c>
-      <c r="G49" s="136"/>
+      <c r="G49" s="124"/>
       <c r="H49" s="53" t="str">
         <f>VLOOKUP(F49,Lookups!$D:$E,2,0)</f>
         <v>Endeavor</v>
@@ -7148,22 +7148,22 @@
       <c r="I49" s="110">
         <v>64</v>
       </c>
-      <c r="J49" s="136">
+      <c r="J49" s="124">
         <v>1</v>
       </c>
-      <c r="K49" s="136"/>
+      <c r="K49" s="124"/>
       <c r="L49" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B24</v>
       </c>
-      <c r="M49" s="139" t="str">
+      <c r="M49" s="141" t="str">
         <f t="shared" si="5"/>
         <v>1B 01 40 01</v>
       </c>
-      <c r="N49" s="139"/>
-      <c r="O49" s="139"/>
-      <c r="P49" s="139"/>
-      <c r="Q49" s="140"/>
+      <c r="N49" s="141"/>
+      <c r="O49" s="141"/>
+      <c r="P49" s="141"/>
+      <c r="Q49" s="142"/>
       <c r="R49" s="70"/>
       <c r="S49" s="51"/>
       <c r="T49" s="51"/>
@@ -7184,10 +7184,10 @@
       <c r="E50" s="59">
         <v>19</v>
       </c>
-      <c r="F50" s="136">
+      <c r="F50" s="124">
         <v>200</v>
       </c>
-      <c r="G50" s="136"/>
+      <c r="G50" s="124"/>
       <c r="H50" s="53" t="str">
         <f>VLOOKUP(F50,Lookups!$D:$E,2,0)</f>
         <v>Outrage</v>
@@ -7195,22 +7195,22 @@
       <c r="I50" s="110">
         <v>48</v>
       </c>
-      <c r="J50" s="136">
+      <c r="J50" s="124">
         <v>1</v>
       </c>
-      <c r="K50" s="136"/>
+      <c r="K50" s="124"/>
       <c r="L50" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B28</v>
       </c>
-      <c r="M50" s="139" t="str">
+      <c r="M50" s="141" t="str">
         <f t="shared" si="5"/>
         <v>C8 00 30 01</v>
       </c>
-      <c r="N50" s="139"/>
-      <c r="O50" s="139"/>
-      <c r="P50" s="139"/>
-      <c r="Q50" s="140"/>
+      <c r="N50" s="141"/>
+      <c r="O50" s="141"/>
+      <c r="P50" s="141"/>
+      <c r="Q50" s="142"/>
       <c r="R50" s="70"/>
       <c r="S50" s="51"/>
       <c r="T50" s="51"/>
@@ -7231,10 +7231,10 @@
       <c r="E51" s="59">
         <v>20</v>
       </c>
-      <c r="F51" s="136">
+      <c r="F51" s="124">
         <v>246</v>
       </c>
-      <c r="G51" s="136"/>
+      <c r="G51" s="124"/>
       <c r="H51" s="53" t="str">
         <f>VLOOKUP(F51,Lookups!$D:$E,2,0)</f>
         <v>AncientPower</v>
@@ -7242,22 +7242,22 @@
       <c r="I51" s="110">
         <v>40</v>
       </c>
-      <c r="J51" s="136">
+      <c r="J51" s="124">
         <v>1</v>
       </c>
-      <c r="K51" s="136"/>
+      <c r="K51" s="124"/>
       <c r="L51" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B2C</v>
       </c>
-      <c r="M51" s="139" t="str">
+      <c r="M51" s="141" t="str">
         <f t="shared" si="5"/>
         <v>F6 00 28 01</v>
       </c>
-      <c r="N51" s="139"/>
-      <c r="O51" s="139"/>
-      <c r="P51" s="139"/>
-      <c r="Q51" s="140"/>
+      <c r="N51" s="141"/>
+      <c r="O51" s="141"/>
+      <c r="P51" s="141"/>
+      <c r="Q51" s="142"/>
       <c r="R51" s="70"/>
       <c r="S51" s="51"/>
       <c r="T51" s="51"/>
@@ -7278,10 +7278,10 @@
       <c r="E52" s="59">
         <v>21</v>
       </c>
-      <c r="F52" s="136">
+      <c r="F52" s="124">
         <v>235</v>
       </c>
-      <c r="G52" s="136"/>
+      <c r="G52" s="124"/>
       <c r="H52" s="53" t="str">
         <f>VLOOKUP(F52,Lookups!$D:$E,2,0)</f>
         <v>Synthesis</v>
@@ -7289,22 +7289,22 @@
       <c r="I52" s="110">
         <v>40</v>
       </c>
-      <c r="J52" s="136">
+      <c r="J52" s="124">
         <v>2</v>
       </c>
-      <c r="K52" s="136"/>
+      <c r="K52" s="124"/>
       <c r="L52" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B30</v>
       </c>
-      <c r="M52" s="139" t="str">
+      <c r="M52" s="141" t="str">
         <f t="shared" si="5"/>
         <v>EB 00 28 02</v>
       </c>
-      <c r="N52" s="139"/>
-      <c r="O52" s="139"/>
-      <c r="P52" s="139"/>
-      <c r="Q52" s="140"/>
+      <c r="N52" s="141"/>
+      <c r="O52" s="141"/>
+      <c r="P52" s="141"/>
+      <c r="Q52" s="142"/>
       <c r="R52" s="70"/>
       <c r="S52" s="51"/>
       <c r="T52" s="51"/>
@@ -7325,10 +7325,10 @@
       <c r="E53" s="59">
         <v>22</v>
       </c>
-      <c r="F53" s="136">
+      <c r="F53" s="124">
         <v>324</v>
       </c>
-      <c r="G53" s="136"/>
+      <c r="G53" s="124"/>
       <c r="H53" s="53" t="str">
         <f>VLOOKUP(F53,Lookups!$D:$E,2,0)</f>
         <v>Signal Beam</v>
@@ -7336,22 +7336,22 @@
       <c r="I53" s="110">
         <v>40</v>
       </c>
-      <c r="J53" s="136">
+      <c r="J53" s="124">
         <v>1</v>
       </c>
-      <c r="K53" s="136"/>
+      <c r="K53" s="124"/>
       <c r="L53" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B34</v>
       </c>
-      <c r="M53" s="139" t="str">
+      <c r="M53" s="141" t="str">
         <f t="shared" si="5"/>
         <v>44 01 28 01</v>
       </c>
-      <c r="N53" s="139"/>
-      <c r="O53" s="139"/>
-      <c r="P53" s="139"/>
-      <c r="Q53" s="140"/>
+      <c r="N53" s="141"/>
+      <c r="O53" s="141"/>
+      <c r="P53" s="141"/>
+      <c r="Q53" s="142"/>
       <c r="R53" s="70"/>
       <c r="S53" s="51"/>
       <c r="T53" s="51"/>
@@ -7372,10 +7372,10 @@
       <c r="E54" s="59">
         <v>23</v>
       </c>
-      <c r="F54" s="136">
+      <c r="F54" s="124">
         <v>428</v>
       </c>
-      <c r="G54" s="136"/>
+      <c r="G54" s="124"/>
       <c r="H54" s="53" t="str">
         <f>VLOOKUP(F54,Lookups!$D:$E,2,0)</f>
         <v>Zen Headbutt</v>
@@ -7383,22 +7383,22 @@
       <c r="I54" s="110">
         <v>64</v>
       </c>
-      <c r="J54" s="136">
+      <c r="J54" s="124">
         <v>0</v>
       </c>
-      <c r="K54" s="136"/>
+      <c r="K54" s="124"/>
       <c r="L54" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B38</v>
       </c>
-      <c r="M54" s="139" t="str">
+      <c r="M54" s="141" t="str">
         <f t="shared" si="5"/>
         <v>AC 01 40 00</v>
       </c>
-      <c r="N54" s="139"/>
-      <c r="O54" s="139"/>
-      <c r="P54" s="139"/>
-      <c r="Q54" s="140"/>
+      <c r="N54" s="141"/>
+      <c r="O54" s="141"/>
+      <c r="P54" s="141"/>
+      <c r="Q54" s="142"/>
       <c r="R54" s="70"/>
       <c r="S54" s="51"/>
       <c r="T54" s="51"/>
@@ -7419,10 +7419,10 @@
       <c r="E55" s="59">
         <v>24</v>
       </c>
-      <c r="F55" s="136">
+      <c r="F55" s="124">
         <v>410</v>
       </c>
-      <c r="G55" s="136"/>
+      <c r="G55" s="124"/>
       <c r="H55" s="53" t="str">
         <f>VLOOKUP(F55,Lookups!$D:$E,2,0)</f>
         <v>Vacuum Wave</v>
@@ -7430,22 +7430,22 @@
       <c r="I55" s="110">
         <v>48</v>
       </c>
-      <c r="J55" s="136">
+      <c r="J55" s="124">
         <v>0</v>
       </c>
-      <c r="K55" s="136"/>
+      <c r="K55" s="124"/>
       <c r="L55" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B3C</v>
       </c>
-      <c r="M55" s="139" t="str">
+      <c r="M55" s="141" t="str">
         <f t="shared" si="5"/>
         <v>9A 01 30 00</v>
       </c>
-      <c r="N55" s="139"/>
-      <c r="O55" s="139"/>
-      <c r="P55" s="139"/>
-      <c r="Q55" s="140"/>
+      <c r="N55" s="141"/>
+      <c r="O55" s="141"/>
+      <c r="P55" s="141"/>
+      <c r="Q55" s="142"/>
       <c r="R55" s="70"/>
       <c r="S55" s="51"/>
       <c r="T55" s="51"/>
@@ -7466,10 +7466,10 @@
       <c r="E56" s="59">
         <v>25</v>
       </c>
-      <c r="F56" s="136">
+      <c r="F56" s="124">
         <v>414</v>
       </c>
-      <c r="G56" s="136"/>
+      <c r="G56" s="124"/>
       <c r="H56" s="53" t="str">
         <f>VLOOKUP(F56,Lookups!$D:$E,2,0)</f>
         <v>Earth Power</v>
@@ -7477,22 +7477,22 @@
       <c r="I56" s="110">
         <v>40</v>
       </c>
-      <c r="J56" s="136">
+      <c r="J56" s="124">
         <v>1</v>
       </c>
-      <c r="K56" s="136"/>
+      <c r="K56" s="124"/>
       <c r="L56" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B40</v>
       </c>
-      <c r="M56" s="139" t="str">
+      <c r="M56" s="141" t="str">
         <f t="shared" si="5"/>
         <v>9E 01 28 01</v>
       </c>
-      <c r="N56" s="139"/>
-      <c r="O56" s="139"/>
-      <c r="P56" s="139"/>
-      <c r="Q56" s="140"/>
+      <c r="N56" s="141"/>
+      <c r="O56" s="141"/>
+      <c r="P56" s="141"/>
+      <c r="Q56" s="142"/>
       <c r="R56" s="70"/>
       <c r="S56" s="51"/>
       <c r="T56" s="51"/>
@@ -7513,10 +7513,10 @@
       <c r="E57" s="59">
         <v>26</v>
       </c>
-      <c r="F57" s="136">
+      <c r="F57" s="124">
         <v>441</v>
       </c>
-      <c r="G57" s="136"/>
+      <c r="G57" s="124"/>
       <c r="H57" s="53" t="str">
         <f>VLOOKUP(F57,Lookups!$D:$E,2,0)</f>
         <v>Gunk Shot</v>
@@ -7524,22 +7524,22 @@
       <c r="I57" s="110">
         <v>32</v>
       </c>
-      <c r="J57" s="136">
+      <c r="J57" s="124">
         <v>1</v>
       </c>
-      <c r="K57" s="136"/>
+      <c r="K57" s="124"/>
       <c r="L57" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B44</v>
       </c>
-      <c r="M57" s="139" t="str">
+      <c r="M57" s="141" t="str">
         <f t="shared" si="5"/>
         <v>B9 01 20 01</v>
       </c>
-      <c r="N57" s="139"/>
-      <c r="O57" s="139"/>
-      <c r="P57" s="139"/>
-      <c r="Q57" s="140"/>
+      <c r="N57" s="141"/>
+      <c r="O57" s="141"/>
+      <c r="P57" s="141"/>
+      <c r="Q57" s="142"/>
       <c r="R57" s="70"/>
       <c r="S57" s="51"/>
       <c r="T57" s="51"/>
@@ -7560,10 +7560,10 @@
       <c r="E58" s="59">
         <v>27</v>
       </c>
-      <c r="F58" s="136">
+      <c r="F58" s="124">
         <v>239</v>
       </c>
-      <c r="G58" s="136"/>
+      <c r="G58" s="124"/>
       <c r="H58" s="53" t="str">
         <f>VLOOKUP(F58,Lookups!$D:$E,2,0)</f>
         <v>Twister</v>
@@ -7571,22 +7571,22 @@
       <c r="I58" s="110">
         <v>40</v>
       </c>
-      <c r="J58" s="136">
+      <c r="J58" s="124">
         <v>1</v>
       </c>
-      <c r="K58" s="136"/>
+      <c r="K58" s="124"/>
       <c r="L58" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B48</v>
       </c>
-      <c r="M58" s="139" t="str">
+      <c r="M58" s="141" t="str">
         <f t="shared" si="5"/>
         <v>EF 00 28 01</v>
       </c>
-      <c r="N58" s="139"/>
-      <c r="O58" s="139"/>
-      <c r="P58" s="139"/>
-      <c r="Q58" s="140"/>
+      <c r="N58" s="141"/>
+      <c r="O58" s="141"/>
+      <c r="P58" s="141"/>
+      <c r="Q58" s="142"/>
       <c r="R58" s="70"/>
       <c r="S58" s="51"/>
       <c r="T58" s="51"/>
@@ -7607,10 +7607,10 @@
       <c r="E59" s="59">
         <v>28</v>
       </c>
-      <c r="F59" s="136">
+      <c r="F59" s="124">
         <v>402</v>
       </c>
-      <c r="G59" s="136"/>
+      <c r="G59" s="124"/>
       <c r="H59" s="53" t="str">
         <f>VLOOKUP(F59,Lookups!$D:$E,2,0)</f>
         <v>Seed Bomb</v>
@@ -7618,22 +7618,22 @@
       <c r="I59" s="110">
         <v>40</v>
       </c>
-      <c r="J59" s="136">
+      <c r="J59" s="124">
         <v>1</v>
       </c>
-      <c r="K59" s="136"/>
+      <c r="K59" s="124"/>
       <c r="L59" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B4C</v>
       </c>
-      <c r="M59" s="139" t="str">
+      <c r="M59" s="141" t="str">
         <f t="shared" si="5"/>
         <v>92 01 28 01</v>
       </c>
-      <c r="N59" s="139"/>
-      <c r="O59" s="139"/>
-      <c r="P59" s="139"/>
-      <c r="Q59" s="140"/>
+      <c r="N59" s="141"/>
+      <c r="O59" s="141"/>
+      <c r="P59" s="141"/>
+      <c r="Q59" s="142"/>
       <c r="R59" s="70"/>
       <c r="S59" s="51"/>
       <c r="T59" s="51"/>
@@ -7654,10 +7654,10 @@
       <c r="E60" s="59">
         <v>29</v>
       </c>
-      <c r="F60" s="136">
+      <c r="F60" s="124">
         <v>334</v>
       </c>
-      <c r="G60" s="136"/>
+      <c r="G60" s="124"/>
       <c r="H60" s="53" t="str">
         <f>VLOOKUP(F60,Lookups!$D:$E,2,0)</f>
         <v>Iron Defense</v>
@@ -7665,22 +7665,22 @@
       <c r="I60" s="110">
         <v>40</v>
       </c>
-      <c r="J60" s="136">
+      <c r="J60" s="124">
         <v>1</v>
       </c>
-      <c r="K60" s="136"/>
+      <c r="K60" s="124"/>
       <c r="L60" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B50</v>
       </c>
-      <c r="M60" s="139" t="str">
+      <c r="M60" s="141" t="str">
         <f t="shared" si="5"/>
         <v>4E 01 28 01</v>
       </c>
-      <c r="N60" s="139"/>
-      <c r="O60" s="139"/>
-      <c r="P60" s="139"/>
-      <c r="Q60" s="140"/>
+      <c r="N60" s="141"/>
+      <c r="O60" s="141"/>
+      <c r="P60" s="141"/>
+      <c r="Q60" s="142"/>
       <c r="R60" s="70"/>
       <c r="S60" s="51"/>
       <c r="T60" s="51"/>
@@ -7701,10 +7701,10 @@
       <c r="E61" s="59">
         <v>30</v>
       </c>
-      <c r="F61" s="136">
+      <c r="F61" s="124">
         <v>393</v>
       </c>
-      <c r="G61" s="136"/>
+      <c r="G61" s="124"/>
       <c r="H61" s="53" t="str">
         <f>VLOOKUP(F61,Lookups!$D:$E,2,0)</f>
         <v>Magnet Rise</v>
@@ -7712,22 +7712,22 @@
       <c r="I61" s="110">
         <v>40</v>
       </c>
-      <c r="J61" s="136">
+      <c r="J61" s="124">
         <v>2</v>
       </c>
-      <c r="K61" s="136"/>
+      <c r="K61" s="124"/>
       <c r="L61" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B54</v>
       </c>
-      <c r="M61" s="139" t="str">
+      <c r="M61" s="141" t="str">
         <f t="shared" si="5"/>
         <v>89 01 28 02</v>
       </c>
-      <c r="N61" s="139"/>
-      <c r="O61" s="139"/>
-      <c r="P61" s="139"/>
-      <c r="Q61" s="140"/>
+      <c r="N61" s="141"/>
+      <c r="O61" s="141"/>
+      <c r="P61" s="141"/>
+      <c r="Q61" s="142"/>
       <c r="R61" s="70"/>
       <c r="S61" s="51"/>
       <c r="T61" s="51"/>
@@ -7748,10 +7748,10 @@
       <c r="E62" s="59">
         <v>31</v>
       </c>
-      <c r="F62" s="136">
+      <c r="F62" s="124">
         <v>387</v>
       </c>
-      <c r="G62" s="136"/>
+      <c r="G62" s="124"/>
       <c r="H62" s="53" t="str">
         <f>VLOOKUP(F62,Lookups!$D:$E,2,0)</f>
         <v>Last Resort</v>
@@ -7759,22 +7759,22 @@
       <c r="I62" s="110">
         <v>48</v>
       </c>
-      <c r="J62" s="136">
+      <c r="J62" s="124">
         <v>2</v>
       </c>
-      <c r="K62" s="136"/>
+      <c r="K62" s="124"/>
       <c r="L62" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B58</v>
       </c>
-      <c r="M62" s="139" t="str">
+      <c r="M62" s="141" t="str">
         <f t="shared" si="5"/>
         <v>83 01 30 02</v>
       </c>
-      <c r="N62" s="139"/>
-      <c r="O62" s="139"/>
-      <c r="P62" s="139"/>
-      <c r="Q62" s="140"/>
+      <c r="N62" s="141"/>
+      <c r="O62" s="141"/>
+      <c r="P62" s="141"/>
+      <c r="Q62" s="142"/>
       <c r="R62" s="70"/>
       <c r="S62" s="51"/>
       <c r="T62" s="51"/>
@@ -7795,10 +7795,10 @@
       <c r="E63" s="59">
         <v>32</v>
       </c>
-      <c r="F63" s="136">
+      <c r="F63" s="124">
         <v>340</v>
       </c>
-      <c r="G63" s="136"/>
+      <c r="G63" s="124"/>
       <c r="H63" s="53" t="str">
         <f>VLOOKUP(F63,Lookups!$D:$E,2,0)</f>
         <v>Bounce</v>
@@ -7806,22 +7806,22 @@
       <c r="I63" s="110">
         <v>32</v>
       </c>
-      <c r="J63" s="136">
+      <c r="J63" s="124">
         <v>1</v>
       </c>
-      <c r="K63" s="136"/>
+      <c r="K63" s="124"/>
       <c r="L63" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B5C</v>
       </c>
-      <c r="M63" s="139" t="str">
+      <c r="M63" s="141" t="str">
         <f t="shared" si="5"/>
         <v>54 01 20 01</v>
       </c>
-      <c r="N63" s="139"/>
-      <c r="O63" s="139"/>
-      <c r="P63" s="139"/>
-      <c r="Q63" s="140"/>
+      <c r="N63" s="141"/>
+      <c r="O63" s="141"/>
+      <c r="P63" s="141"/>
+      <c r="Q63" s="142"/>
       <c r="R63" s="70"/>
       <c r="S63" s="51"/>
       <c r="T63" s="51"/>
@@ -7842,10 +7842,10 @@
       <c r="E64" s="59">
         <v>33</v>
       </c>
-      <c r="F64" s="136">
+      <c r="F64" s="124">
         <v>271</v>
       </c>
-      <c r="G64" s="136"/>
+      <c r="G64" s="124"/>
       <c r="H64" s="53" t="str">
         <f>VLOOKUP(F64,Lookups!$D:$E,2,0)</f>
         <v>Trick</v>
@@ -7853,22 +7853,22 @@
       <c r="I64" s="110">
         <v>48</v>
       </c>
-      <c r="J64" s="136">
+      <c r="J64" s="124">
         <v>0</v>
       </c>
-      <c r="K64" s="136"/>
+      <c r="K64" s="124"/>
       <c r="L64" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B60</v>
       </c>
-      <c r="M64" s="139" t="str">
+      <c r="M64" s="141" t="str">
         <f t="shared" si="5"/>
         <v>0F 01 30 00</v>
       </c>
-      <c r="N64" s="139"/>
-      <c r="O64" s="139"/>
-      <c r="P64" s="139"/>
-      <c r="Q64" s="140"/>
+      <c r="N64" s="141"/>
+      <c r="O64" s="141"/>
+      <c r="P64" s="141"/>
+      <c r="Q64" s="142"/>
       <c r="R64" s="70"/>
       <c r="S64" s="51"/>
       <c r="T64" s="51"/>
@@ -7889,10 +7889,10 @@
       <c r="E65" s="59">
         <v>34</v>
       </c>
-      <c r="F65" s="136">
+      <c r="F65" s="124">
         <v>257</v>
       </c>
-      <c r="G65" s="136"/>
+      <c r="G65" s="124"/>
       <c r="H65" s="53" t="str">
         <f>VLOOKUP(F65,Lookups!$D:$E,2,0)</f>
         <v>Heat Wave</v>
@@ -7900,22 +7900,22 @@
       <c r="I65" s="110">
         <v>48</v>
       </c>
-      <c r="J65" s="136">
+      <c r="J65" s="124">
         <v>1</v>
       </c>
-      <c r="K65" s="136"/>
+      <c r="K65" s="124"/>
       <c r="L65" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B64</v>
       </c>
-      <c r="M65" s="139" t="str">
+      <c r="M65" s="141" t="str">
         <f t="shared" si="5"/>
         <v>01 01 30 01</v>
       </c>
-      <c r="N65" s="139"/>
-      <c r="O65" s="139"/>
-      <c r="P65" s="139"/>
-      <c r="Q65" s="140"/>
+      <c r="N65" s="141"/>
+      <c r="O65" s="141"/>
+      <c r="P65" s="141"/>
+      <c r="Q65" s="142"/>
       <c r="R65" s="70"/>
       <c r="S65" s="51"/>
       <c r="T65" s="51"/>
@@ -7936,10 +7936,10 @@
       <c r="E66" s="59">
         <v>35</v>
       </c>
-      <c r="F66" s="136">
+      <c r="F66" s="124">
         <v>282</v>
       </c>
-      <c r="G66" s="136"/>
+      <c r="G66" s="124"/>
       <c r="H66" s="53" t="str">
         <f>VLOOKUP(F66,Lookups!$D:$E,2,0)</f>
         <v>Knock Off</v>
@@ -7947,22 +7947,22 @@
       <c r="I66" s="110">
         <v>40</v>
       </c>
-      <c r="J66" s="136">
+      <c r="J66" s="124">
         <v>0</v>
       </c>
-      <c r="K66" s="136"/>
+      <c r="K66" s="124"/>
       <c r="L66" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B68</v>
       </c>
-      <c r="M66" s="139" t="str">
+      <c r="M66" s="141" t="str">
         <f t="shared" si="5"/>
         <v>1A 01 28 00</v>
       </c>
-      <c r="N66" s="139"/>
-      <c r="O66" s="139"/>
-      <c r="P66" s="139"/>
-      <c r="Q66" s="140"/>
+      <c r="N66" s="141"/>
+      <c r="O66" s="141"/>
+      <c r="P66" s="141"/>
+      <c r="Q66" s="142"/>
       <c r="R66" s="70"/>
       <c r="S66" s="51"/>
       <c r="T66" s="51"/>
@@ -7983,10 +7983,10 @@
       <c r="E67" s="59">
         <v>36</v>
       </c>
-      <c r="F67" s="136">
+      <c r="F67" s="124">
         <v>389</v>
       </c>
-      <c r="G67" s="136"/>
+      <c r="G67" s="124"/>
       <c r="H67" s="53" t="str">
         <f>VLOOKUP(F67,Lookups!$D:$E,2,0)</f>
         <v>Sucker Punch</v>
@@ -7994,22 +7994,22 @@
       <c r="I67" s="110">
         <v>40</v>
       </c>
-      <c r="J67" s="136">
+      <c r="J67" s="124">
         <v>0</v>
       </c>
-      <c r="K67" s="136"/>
+      <c r="K67" s="124"/>
       <c r="L67" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B6C</v>
       </c>
-      <c r="M67" s="139" t="str">
+      <c r="M67" s="141" t="str">
         <f t="shared" si="5"/>
         <v>85 01 28 00</v>
       </c>
-      <c r="N67" s="139"/>
-      <c r="O67" s="139"/>
-      <c r="P67" s="139"/>
-      <c r="Q67" s="140"/>
+      <c r="N67" s="141"/>
+      <c r="O67" s="141"/>
+      <c r="P67" s="141"/>
+      <c r="Q67" s="142"/>
       <c r="R67" s="70"/>
       <c r="S67" s="51"/>
       <c r="T67" s="51"/>
@@ -8030,10 +8030,10 @@
       <c r="E68" s="59">
         <v>37</v>
       </c>
-      <c r="F68" s="136">
+      <c r="F68" s="124">
         <v>129</v>
       </c>
-      <c r="G68" s="136"/>
+      <c r="G68" s="124"/>
       <c r="H68" s="53" t="str">
         <f>VLOOKUP(F68,Lookups!$D:$E,2,0)</f>
         <v>Swift</v>
@@ -8041,22 +8041,22 @@
       <c r="I68" s="110">
         <v>40</v>
       </c>
-      <c r="J68" s="136">
+      <c r="J68" s="124">
         <v>2</v>
       </c>
-      <c r="K68" s="136"/>
+      <c r="K68" s="124"/>
       <c r="L68" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B70</v>
       </c>
-      <c r="M68" s="139" t="str">
+      <c r="M68" s="141" t="str">
         <f t="shared" si="5"/>
         <v>81 00 28 02</v>
       </c>
-      <c r="N68" s="139"/>
-      <c r="O68" s="139"/>
-      <c r="P68" s="139"/>
-      <c r="Q68" s="140"/>
+      <c r="N68" s="141"/>
+      <c r="O68" s="141"/>
+      <c r="P68" s="141"/>
+      <c r="Q68" s="142"/>
       <c r="R68" s="70"/>
       <c r="S68" s="51"/>
       <c r="T68" s="51"/>
@@ -8077,10 +8077,10 @@
       <c r="E69" s="59">
         <v>38</v>
       </c>
-      <c r="F69" s="136">
+      <c r="F69" s="124">
         <v>253</v>
       </c>
-      <c r="G69" s="136"/>
+      <c r="G69" s="124"/>
       <c r="H69" s="53" t="str">
         <f>VLOOKUP(F69,Lookups!$D:$E,2,0)</f>
         <v>Uproar</v>
@@ -8088,22 +8088,22 @@
       <c r="I69" s="110">
         <v>48</v>
       </c>
-      <c r="J69" s="136">
+      <c r="J69" s="124">
         <v>2</v>
       </c>
-      <c r="K69" s="136"/>
+      <c r="K69" s="124"/>
       <c r="L69" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B74</v>
       </c>
-      <c r="M69" s="139" t="str">
+      <c r="M69" s="141" t="str">
         <f t="shared" si="5"/>
         <v>FD 00 30 02</v>
       </c>
-      <c r="N69" s="139"/>
-      <c r="O69" s="139"/>
-      <c r="P69" s="139"/>
-      <c r="Q69" s="140"/>
+      <c r="N69" s="141"/>
+      <c r="O69" s="141"/>
+      <c r="P69" s="141"/>
+      <c r="Q69" s="142"/>
       <c r="R69" s="70"/>
       <c r="S69" s="51"/>
       <c r="T69" s="51"/>
@@ -8124,10 +8124,10 @@
       <c r="E70" s="59">
         <v>39</v>
       </c>
-      <c r="F70" s="136">
+      <c r="F70" s="124">
         <v>162</v>
       </c>
-      <c r="G70" s="136"/>
+      <c r="G70" s="124"/>
       <c r="H70" s="53" t="str">
         <f>VLOOKUP(F70,Lookups!$D:$E,2,0)</f>
         <v>Super Fang</v>
@@ -8135,22 +8135,22 @@
       <c r="I70" s="110">
         <v>40</v>
       </c>
-      <c r="J70" s="136">
+      <c r="J70" s="124">
         <v>1</v>
       </c>
-      <c r="K70" s="136"/>
+      <c r="K70" s="124"/>
       <c r="L70" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B78</v>
       </c>
-      <c r="M70" s="139" t="str">
+      <c r="M70" s="141" t="str">
         <f t="shared" si="5"/>
         <v>A2 00 28 01</v>
       </c>
-      <c r="N70" s="139"/>
-      <c r="O70" s="139"/>
-      <c r="P70" s="139"/>
-      <c r="Q70" s="140"/>
+      <c r="N70" s="141"/>
+      <c r="O70" s="141"/>
+      <c r="P70" s="141"/>
+      <c r="Q70" s="142"/>
       <c r="R70" s="70"/>
       <c r="S70" s="51"/>
       <c r="T70" s="51"/>
@@ -8171,10 +8171,10 @@
       <c r="E71" s="59">
         <v>40</v>
       </c>
-      <c r="F71" s="136">
+      <c r="F71" s="124">
         <v>220</v>
       </c>
-      <c r="G71" s="136"/>
+      <c r="G71" s="124"/>
       <c r="H71" s="53" t="str">
         <f>VLOOKUP(F71,Lookups!$D:$E,2,0)</f>
         <v>Pain Split</v>
@@ -8182,22 +8182,22 @@
       <c r="I71" s="110">
         <v>64</v>
       </c>
-      <c r="J71" s="136">
+      <c r="J71" s="124">
         <v>1</v>
       </c>
-      <c r="K71" s="136"/>
+      <c r="K71" s="124"/>
       <c r="L71" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B7C</v>
       </c>
-      <c r="M71" s="139" t="str">
+      <c r="M71" s="141" t="str">
         <f t="shared" si="5"/>
         <v>DC 00 40 01</v>
       </c>
-      <c r="N71" s="139"/>
-      <c r="O71" s="139"/>
-      <c r="P71" s="139"/>
-      <c r="Q71" s="140"/>
+      <c r="N71" s="141"/>
+      <c r="O71" s="141"/>
+      <c r="P71" s="141"/>
+      <c r="Q71" s="142"/>
       <c r="R71" s="70"/>
       <c r="S71" s="51"/>
       <c r="T71" s="51"/>
@@ -8218,10 +8218,10 @@
       <c r="E72" s="59">
         <v>41</v>
       </c>
-      <c r="F72" s="136">
+      <c r="F72" s="124">
         <v>81</v>
       </c>
-      <c r="G72" s="136"/>
+      <c r="G72" s="124"/>
       <c r="H72" s="53" t="str">
         <f>VLOOKUP(F72,Lookups!$D:$E,2,0)</f>
         <v>String Shot</v>
@@ -8229,22 +8229,22 @@
       <c r="I72" s="110">
         <v>32</v>
       </c>
-      <c r="J72" s="136">
+      <c r="J72" s="124">
         <v>2</v>
       </c>
-      <c r="K72" s="136"/>
+      <c r="K72" s="124"/>
       <c r="L72" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B80</v>
       </c>
-      <c r="M72" s="139" t="str">
+      <c r="M72" s="141" t="str">
         <f t="shared" si="5"/>
         <v>51 00 20 02</v>
       </c>
-      <c r="N72" s="139"/>
-      <c r="O72" s="139"/>
-      <c r="P72" s="139"/>
-      <c r="Q72" s="140"/>
+      <c r="N72" s="141"/>
+      <c r="O72" s="141"/>
+      <c r="P72" s="141"/>
+      <c r="Q72" s="142"/>
       <c r="R72" s="70"/>
       <c r="S72" s="51"/>
       <c r="T72" s="51"/>
@@ -8265,10 +8265,10 @@
       <c r="E73" s="59">
         <v>42</v>
       </c>
-      <c r="F73" s="136">
+      <c r="F73" s="124">
         <v>366</v>
       </c>
-      <c r="G73" s="136"/>
+      <c r="G73" s="124"/>
       <c r="H73" s="53" t="str">
         <f>VLOOKUP(F73,Lookups!$D:$E,2,0)</f>
         <v>Tailwind</v>
@@ -8276,22 +8276,22 @@
       <c r="I73" s="110">
         <v>48</v>
       </c>
-      <c r="J73" s="136">
+      <c r="J73" s="124">
         <v>2</v>
       </c>
-      <c r="K73" s="136"/>
+      <c r="K73" s="124"/>
       <c r="L73" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B84</v>
       </c>
-      <c r="M73" s="139" t="str">
+      <c r="M73" s="141" t="str">
         <f t="shared" si="5"/>
         <v>6E 01 30 02</v>
       </c>
-      <c r="N73" s="139"/>
-      <c r="O73" s="139"/>
-      <c r="P73" s="139"/>
-      <c r="Q73" s="140"/>
+      <c r="N73" s="141"/>
+      <c r="O73" s="141"/>
+      <c r="P73" s="141"/>
+      <c r="Q73" s="142"/>
       <c r="R73" s="70"/>
       <c r="S73" s="51"/>
       <c r="T73" s="51"/>
@@ -8312,10 +8312,10 @@
       <c r="E74" s="59">
         <v>43</v>
       </c>
-      <c r="F74" s="136">
+      <c r="F74" s="124">
         <v>356</v>
       </c>
-      <c r="G74" s="136"/>
+      <c r="G74" s="124"/>
       <c r="H74" s="53" t="str">
         <f>VLOOKUP(F74,Lookups!$D:$E,2,0)</f>
         <v>Gravity</v>
@@ -8323,22 +8323,22 @@
       <c r="I74" s="110">
         <v>32</v>
       </c>
-      <c r="J74" s="136">
+      <c r="J74" s="124">
         <v>2</v>
       </c>
-      <c r="K74" s="136"/>
+      <c r="K74" s="124"/>
       <c r="L74" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B88</v>
       </c>
-      <c r="M74" s="139" t="str">
+      <c r="M74" s="141" t="str">
         <f t="shared" si="5"/>
         <v>64 01 20 02</v>
       </c>
-      <c r="N74" s="139"/>
-      <c r="O74" s="139"/>
-      <c r="P74" s="139"/>
-      <c r="Q74" s="140"/>
+      <c r="N74" s="141"/>
+      <c r="O74" s="141"/>
+      <c r="P74" s="141"/>
+      <c r="Q74" s="142"/>
       <c r="R74" s="70"/>
       <c r="S74" s="51"/>
       <c r="T74" s="51"/>
@@ -8359,10 +8359,10 @@
       <c r="E75" s="59">
         <v>44</v>
       </c>
-      <c r="F75" s="136">
+      <c r="F75" s="124">
         <v>388</v>
       </c>
-      <c r="G75" s="136"/>
+      <c r="G75" s="124"/>
       <c r="H75" s="53" t="str">
         <f>VLOOKUP(F75,Lookups!$D:$E,2,0)</f>
         <v>Worry Seed</v>
@@ -8370,22 +8370,22 @@
       <c r="I75" s="110">
         <v>32</v>
       </c>
-      <c r="J75" s="136">
+      <c r="J75" s="124">
         <v>2</v>
       </c>
-      <c r="K75" s="136"/>
+      <c r="K75" s="124"/>
       <c r="L75" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B8C</v>
       </c>
-      <c r="M75" s="139" t="str">
+      <c r="M75" s="141" t="str">
         <f t="shared" si="5"/>
         <v>84 01 20 02</v>
       </c>
-      <c r="N75" s="139"/>
-      <c r="O75" s="139"/>
-      <c r="P75" s="139"/>
-      <c r="Q75" s="140"/>
+      <c r="N75" s="141"/>
+      <c r="O75" s="141"/>
+      <c r="P75" s="141"/>
+      <c r="Q75" s="142"/>
       <c r="R75" s="70"/>
       <c r="S75" s="51"/>
       <c r="T75" s="51"/>
@@ -8406,10 +8406,10 @@
       <c r="E76" s="59">
         <v>45</v>
       </c>
-      <c r="F76" s="136">
+      <c r="F76" s="124">
         <v>277</v>
       </c>
-      <c r="G76" s="136"/>
+      <c r="G76" s="124"/>
       <c r="H76" s="53" t="str">
         <f>VLOOKUP(F76,Lookups!$D:$E,2,0)</f>
         <v>Magic Coat</v>
@@ -8417,22 +8417,22 @@
       <c r="I76" s="110">
         <v>32</v>
       </c>
-      <c r="J76" s="136">
+      <c r="J76" s="124">
         <v>2</v>
       </c>
-      <c r="K76" s="136"/>
+      <c r="K76" s="124"/>
       <c r="L76" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B90</v>
       </c>
-      <c r="M76" s="139" t="str">
+      <c r="M76" s="141" t="str">
         <f t="shared" si="5"/>
         <v>15 01 20 02</v>
       </c>
-      <c r="N76" s="139"/>
-      <c r="O76" s="139"/>
-      <c r="P76" s="139"/>
-      <c r="Q76" s="140"/>
+      <c r="N76" s="141"/>
+      <c r="O76" s="141"/>
+      <c r="P76" s="141"/>
+      <c r="Q76" s="142"/>
       <c r="R76" s="70"/>
       <c r="S76" s="51"/>
       <c r="T76" s="51"/>
@@ -8453,10 +8453,10 @@
       <c r="E77" s="59">
         <v>46</v>
       </c>
-      <c r="F77" s="136">
+      <c r="F77" s="124">
         <v>272</v>
       </c>
-      <c r="G77" s="136"/>
+      <c r="G77" s="124"/>
       <c r="H77" s="53" t="str">
         <f>VLOOKUP(F77,Lookups!$D:$E,2,0)</f>
         <v>Role Play</v>
@@ -8464,22 +8464,22 @@
       <c r="I77" s="110">
         <v>48</v>
       </c>
-      <c r="J77" s="136">
+      <c r="J77" s="124">
         <v>2</v>
       </c>
-      <c r="K77" s="136"/>
+      <c r="K77" s="124"/>
       <c r="L77" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B94</v>
       </c>
-      <c r="M77" s="139" t="str">
+      <c r="M77" s="141" t="str">
         <f t="shared" si="5"/>
         <v>10 01 30 02</v>
       </c>
-      <c r="N77" s="139"/>
-      <c r="O77" s="139"/>
-      <c r="P77" s="139"/>
-      <c r="Q77" s="140"/>
+      <c r="N77" s="141"/>
+      <c r="O77" s="141"/>
+      <c r="P77" s="141"/>
+      <c r="Q77" s="142"/>
       <c r="R77" s="70"/>
       <c r="S77" s="51"/>
       <c r="T77" s="51"/>
@@ -8500,10 +8500,10 @@
       <c r="E78" s="59">
         <v>47</v>
       </c>
-      <c r="F78" s="136">
+      <c r="F78" s="124">
         <v>215</v>
       </c>
-      <c r="G78" s="136"/>
+      <c r="G78" s="124"/>
       <c r="H78" s="53" t="str">
         <f>VLOOKUP(F78,Lookups!$D:$E,2,0)</f>
         <v>Heal Bell</v>
@@ -8511,22 +8511,22 @@
       <c r="I78" s="110">
         <v>48</v>
       </c>
-      <c r="J78" s="136">
+      <c r="J78" s="124">
         <v>2</v>
       </c>
-      <c r="K78" s="136"/>
+      <c r="K78" s="124"/>
       <c r="L78" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B98</v>
       </c>
-      <c r="M78" s="139" t="str">
+      <c r="M78" s="141" t="str">
         <f t="shared" si="5"/>
         <v>D7 00 30 02</v>
       </c>
-      <c r="N78" s="139"/>
-      <c r="O78" s="139"/>
-      <c r="P78" s="139"/>
-      <c r="Q78" s="140"/>
+      <c r="N78" s="141"/>
+      <c r="O78" s="141"/>
+      <c r="P78" s="141"/>
+      <c r="Q78" s="142"/>
       <c r="R78" s="70"/>
       <c r="S78" s="51"/>
       <c r="T78" s="51"/>
@@ -8547,10 +8547,10 @@
       <c r="E79" s="59">
         <v>48</v>
       </c>
-      <c r="F79" s="136">
+      <c r="F79" s="124">
         <v>67</v>
       </c>
-      <c r="G79" s="136"/>
+      <c r="G79" s="124"/>
       <c r="H79" s="53" t="str">
         <f>VLOOKUP(F79,Lookups!$D:$E,2,0)</f>
         <v>Low Kick</v>
@@ -8558,22 +8558,22 @@
       <c r="I79" s="110">
         <v>32</v>
       </c>
-      <c r="J79" s="136">
+      <c r="J79" s="124">
         <v>1</v>
       </c>
-      <c r="K79" s="136"/>
+      <c r="K79" s="124"/>
       <c r="L79" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23B9C</v>
       </c>
-      <c r="M79" s="139" t="str">
+      <c r="M79" s="141" t="str">
         <f t="shared" si="5"/>
         <v>43 00 20 01</v>
       </c>
-      <c r="N79" s="139"/>
-      <c r="O79" s="139"/>
-      <c r="P79" s="139"/>
-      <c r="Q79" s="140"/>
+      <c r="N79" s="141"/>
+      <c r="O79" s="141"/>
+      <c r="P79" s="141"/>
+      <c r="Q79" s="142"/>
       <c r="R79" s="70"/>
       <c r="S79" s="51"/>
       <c r="T79" s="51"/>
@@ -8594,10 +8594,10 @@
       <c r="E80" s="59">
         <v>49</v>
       </c>
-      <c r="F80" s="136">
+      <c r="F80" s="124">
         <v>143</v>
       </c>
-      <c r="G80" s="136"/>
+      <c r="G80" s="124"/>
       <c r="H80" s="53" t="str">
         <f>VLOOKUP(F80,Lookups!$D:$E,2,0)</f>
         <v>Sky Attack</v>
@@ -8605,22 +8605,22 @@
       <c r="I80" s="110">
         <v>64</v>
       </c>
-      <c r="J80" s="136">
+      <c r="J80" s="124">
         <v>1</v>
       </c>
-      <c r="K80" s="136"/>
+      <c r="K80" s="124"/>
       <c r="L80" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23BA0</v>
       </c>
-      <c r="M80" s="139" t="str">
+      <c r="M80" s="141" t="str">
         <f t="shared" si="5"/>
         <v>8F 00 40 01</v>
       </c>
-      <c r="N80" s="139"/>
-      <c r="O80" s="139"/>
-      <c r="P80" s="139"/>
-      <c r="Q80" s="140"/>
+      <c r="N80" s="141"/>
+      <c r="O80" s="141"/>
+      <c r="P80" s="141"/>
+      <c r="Q80" s="142"/>
       <c r="R80" s="70"/>
       <c r="S80" s="51"/>
       <c r="T80" s="101"/>
@@ -8641,10 +8641,10 @@
       <c r="E81" s="59">
         <v>50</v>
       </c>
-      <c r="F81" s="136">
+      <c r="F81" s="124">
         <v>335</v>
       </c>
-      <c r="G81" s="136"/>
+      <c r="G81" s="124"/>
       <c r="H81" s="53" t="str">
         <f>VLOOKUP(F81,Lookups!$D:$E,2,0)</f>
         <v>Block</v>
@@ -8652,22 +8652,22 @@
       <c r="I81" s="110">
         <v>32</v>
       </c>
-      <c r="J81" s="136">
+      <c r="J81" s="124">
         <v>2</v>
       </c>
-      <c r="K81" s="136"/>
+      <c r="K81" s="124"/>
       <c r="L81" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23BA4</v>
       </c>
-      <c r="M81" s="139" t="str">
+      <c r="M81" s="141" t="str">
         <f t="shared" si="5"/>
         <v>4F 01 20 02</v>
       </c>
-      <c r="N81" s="139"/>
-      <c r="O81" s="139"/>
-      <c r="P81" s="139"/>
-      <c r="Q81" s="140"/>
+      <c r="N81" s="141"/>
+      <c r="O81" s="141"/>
+      <c r="P81" s="141"/>
+      <c r="Q81" s="142"/>
       <c r="R81" s="70"/>
       <c r="S81" s="51"/>
       <c r="T81" s="101"/>
@@ -8688,10 +8688,10 @@
       <c r="E82" s="59">
         <v>51</v>
       </c>
-      <c r="F82" s="136">
+      <c r="F82" s="124">
         <v>450</v>
       </c>
-      <c r="G82" s="136"/>
+      <c r="G82" s="124"/>
       <c r="H82" s="53" t="str">
         <f>VLOOKUP(F82,Lookups!$D:$E,2,0)</f>
         <v>Bug Bite</v>
@@ -8699,22 +8699,22 @@
       <c r="I82" s="110">
         <v>32</v>
       </c>
-      <c r="J82" s="136">
+      <c r="J82" s="124">
         <v>0</v>
       </c>
-      <c r="K82" s="136"/>
+      <c r="K82" s="124"/>
       <c r="L82" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23BA8</v>
       </c>
-      <c r="M82" s="139" t="str">
+      <c r="M82" s="141" t="str">
         <f t="shared" si="5"/>
         <v>C2 01 20 00</v>
       </c>
-      <c r="N82" s="139"/>
-      <c r="O82" s="139"/>
-      <c r="P82" s="139"/>
-      <c r="Q82" s="140"/>
+      <c r="N82" s="141"/>
+      <c r="O82" s="141"/>
+      <c r="P82" s="141"/>
+      <c r="Q82" s="142"/>
       <c r="R82" s="70"/>
       <c r="S82" s="51"/>
       <c r="T82" s="101"/>
@@ -8735,10 +8735,10 @@
       <c r="E83" s="59">
         <v>52</v>
       </c>
-      <c r="F83" s="136">
+      <c r="F83" s="124">
         <v>29</v>
       </c>
-      <c r="G83" s="136"/>
+      <c r="G83" s="124"/>
       <c r="H83" s="53" t="str">
         <f>VLOOKUP(F83,Lookups!$D:$E,2,0)</f>
         <v>Headbutt</v>
@@ -8746,22 +8746,22 @@
       <c r="I83" s="110">
         <v>0</v>
       </c>
-      <c r="J83" s="136">
+      <c r="J83" s="124">
         <v>3</v>
       </c>
-      <c r="K83" s="136"/>
+      <c r="K83" s="124"/>
       <c r="L83" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23BAC</v>
       </c>
-      <c r="M83" s="139" t="str">
+      <c r="M83" s="141" t="str">
         <f t="shared" si="5"/>
         <v>1D 00 00 03</v>
       </c>
-      <c r="N83" s="139"/>
-      <c r="O83" s="139"/>
-      <c r="P83" s="139"/>
-      <c r="Q83" s="140"/>
+      <c r="N83" s="141"/>
+      <c r="O83" s="141"/>
+      <c r="P83" s="141"/>
+      <c r="Q83" s="142"/>
       <c r="R83" s="70"/>
       <c r="S83" s="51"/>
       <c r="T83" s="101"/>
@@ -8782,10 +8782,10 @@
       <c r="E84" s="59">
         <v>53</v>
       </c>
-      <c r="F84" s="136">
+      <c r="F84" s="124">
         <v>4096</v>
       </c>
-      <c r="G84" s="136"/>
+      <c r="G84" s="124"/>
       <c r="H84" s="53" t="str">
         <f>VLOOKUP(F84,Lookups!$D:$E,2,0)</f>
         <v>Unused</v>
@@ -8793,25 +8793,25 @@
       <c r="I84" s="110">
         <v>0</v>
       </c>
-      <c r="J84" s="136">
+      <c r="J84" s="124">
         <v>0</v>
       </c>
-      <c r="K84" s="136"/>
+      <c r="K84" s="124"/>
       <c r="L84" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23BB0</v>
       </c>
-      <c r="M84" s="139" t="str">
+      <c r="M84" s="141" t="str">
         <f t="shared" si="5"/>
         <v>00 10 00 00</v>
       </c>
-      <c r="N84" s="139"/>
-      <c r="O84" s="139"/>
-      <c r="P84" s="139"/>
-      <c r="Q84" s="140"/>
+      <c r="N84" s="141"/>
+      <c r="O84" s="141"/>
+      <c r="P84" s="141"/>
+      <c r="Q84" s="142"/>
       <c r="R84" s="70"/>
       <c r="S84" s="51"/>
-      <c r="T84" s="143"/>
+      <c r="T84" s="123"/>
       <c r="U84" s="51"/>
       <c r="V84" s="51"/>
       <c r="W84" s="51"/>
@@ -8829,10 +8829,10 @@
       <c r="E85" s="59">
         <v>54</v>
       </c>
-      <c r="F85" s="136">
+      <c r="F85" s="124">
         <v>4096</v>
       </c>
-      <c r="G85" s="136"/>
+      <c r="G85" s="124"/>
       <c r="H85" s="53" t="str">
         <f>VLOOKUP(F85,Lookups!$D:$E,2,0)</f>
         <v>Unused</v>
@@ -8840,25 +8840,25 @@
       <c r="I85" s="110">
         <v>0</v>
       </c>
-      <c r="J85" s="136">
+      <c r="J85" s="124">
         <v>0</v>
       </c>
-      <c r="K85" s="136"/>
+      <c r="K85" s="124"/>
       <c r="L85" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23BB4</v>
       </c>
-      <c r="M85" s="139" t="str">
+      <c r="M85" s="141" t="str">
         <f t="shared" si="5"/>
         <v>00 10 00 00</v>
       </c>
-      <c r="N85" s="139"/>
-      <c r="O85" s="139"/>
-      <c r="P85" s="139"/>
-      <c r="Q85" s="140"/>
+      <c r="N85" s="141"/>
+      <c r="O85" s="141"/>
+      <c r="P85" s="141"/>
+      <c r="Q85" s="142"/>
       <c r="R85" s="70"/>
       <c r="S85" s="51"/>
-      <c r="T85" s="143"/>
+      <c r="T85" s="123"/>
       <c r="U85" s="51"/>
       <c r="V85" s="51"/>
       <c r="W85" s="51"/>
@@ -8876,10 +8876,10 @@
       <c r="E86" s="59">
         <v>55</v>
       </c>
-      <c r="F86" s="136">
+      <c r="F86" s="124">
         <v>4096</v>
       </c>
-      <c r="G86" s="136"/>
+      <c r="G86" s="124"/>
       <c r="H86" s="53" t="str">
         <f>VLOOKUP(F86,Lookups!$D:$E,2,0)</f>
         <v>Unused</v>
@@ -8887,25 +8887,25 @@
       <c r="I86" s="110">
         <v>0</v>
       </c>
-      <c r="J86" s="136">
+      <c r="J86" s="124">
         <v>0</v>
       </c>
-      <c r="K86" s="136"/>
+      <c r="K86" s="124"/>
       <c r="L86" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23BB8</v>
       </c>
-      <c r="M86" s="139" t="str">
+      <c r="M86" s="141" t="str">
         <f t="shared" si="5"/>
         <v>00 10 00 00</v>
       </c>
-      <c r="N86" s="139"/>
-      <c r="O86" s="139"/>
-      <c r="P86" s="139"/>
-      <c r="Q86" s="140"/>
+      <c r="N86" s="141"/>
+      <c r="O86" s="141"/>
+      <c r="P86" s="141"/>
+      <c r="Q86" s="142"/>
       <c r="R86" s="70"/>
       <c r="S86" s="51"/>
-      <c r="T86" s="143"/>
+      <c r="T86" s="123"/>
       <c r="U86" s="51"/>
       <c r="V86" s="51"/>
       <c r="W86" s="51"/>
@@ -8923,10 +8923,10 @@
       <c r="E87" s="59">
         <v>56</v>
       </c>
-      <c r="F87" s="136">
+      <c r="F87" s="124">
         <v>4096</v>
       </c>
-      <c r="G87" s="136"/>
+      <c r="G87" s="124"/>
       <c r="H87" s="53" t="str">
         <f>VLOOKUP(F87,Lookups!$D:$E,2,0)</f>
         <v>Unused</v>
@@ -8934,25 +8934,25 @@
       <c r="I87" s="110">
         <v>0</v>
       </c>
-      <c r="J87" s="136">
+      <c r="J87" s="124">
         <v>0</v>
       </c>
-      <c r="K87" s="136"/>
+      <c r="K87" s="124"/>
       <c r="L87" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23BBC</v>
       </c>
-      <c r="M87" s="139" t="str">
+      <c r="M87" s="141" t="str">
         <f t="shared" si="5"/>
         <v>00 10 00 00</v>
       </c>
-      <c r="N87" s="139"/>
-      <c r="O87" s="139"/>
-      <c r="P87" s="139"/>
-      <c r="Q87" s="140"/>
+      <c r="N87" s="141"/>
+      <c r="O87" s="141"/>
+      <c r="P87" s="141"/>
+      <c r="Q87" s="142"/>
       <c r="R87" s="70"/>
       <c r="S87" s="51"/>
-      <c r="T87" s="143"/>
+      <c r="T87" s="123"/>
       <c r="U87" s="51"/>
       <c r="V87" s="51"/>
       <c r="W87" s="51"/>
@@ -8970,10 +8970,10 @@
       <c r="E88" s="59">
         <v>57</v>
       </c>
-      <c r="F88" s="136">
+      <c r="F88" s="124">
         <v>4096</v>
       </c>
-      <c r="G88" s="136"/>
+      <c r="G88" s="124"/>
       <c r="H88" s="53" t="str">
         <f>VLOOKUP(F88,Lookups!$D:$E,2,0)</f>
         <v>Unused</v>
@@ -8981,25 +8981,25 @@
       <c r="I88" s="110">
         <v>0</v>
       </c>
-      <c r="J88" s="136">
+      <c r="J88" s="124">
         <v>0</v>
       </c>
-      <c r="K88" s="136"/>
+      <c r="K88" s="124"/>
       <c r="L88" s="117" t="str">
         <f t="shared" si="4"/>
         <v>23BC0</v>
       </c>
-      <c r="M88" s="139" t="str">
+      <c r="M88" s="141" t="str">
         <f t="shared" si="5"/>
         <v>00 10 00 00</v>
       </c>
-      <c r="N88" s="139"/>
-      <c r="O88" s="139"/>
-      <c r="P88" s="139"/>
-      <c r="Q88" s="140"/>
+      <c r="N88" s="141"/>
+      <c r="O88" s="141"/>
+      <c r="P88" s="141"/>
+      <c r="Q88" s="142"/>
       <c r="R88" s="70"/>
       <c r="S88" s="51"/>
-      <c r="T88" s="143"/>
+      <c r="T88" s="123"/>
       <c r="U88" s="51"/>
       <c r="V88" s="51"/>
       <c r="W88" s="51"/>
@@ -9017,10 +9017,10 @@
       <c r="E89" s="60">
         <v>58</v>
       </c>
-      <c r="F89" s="137">
+      <c r="F89" s="145">
         <v>4096</v>
       </c>
-      <c r="G89" s="137"/>
+      <c r="G89" s="145"/>
       <c r="H89" s="61" t="str">
         <f>VLOOKUP(F89,Lookups!$D:$E,2,0)</f>
         <v>Unused</v>
@@ -9028,25 +9028,25 @@
       <c r="I89" s="111">
         <v>0</v>
       </c>
-      <c r="J89" s="137">
+      <c r="J89" s="145">
         <v>0</v>
       </c>
-      <c r="K89" s="137"/>
+      <c r="K89" s="145"/>
       <c r="L89" s="122" t="str">
         <f t="shared" si="4"/>
         <v>23BC4</v>
       </c>
-      <c r="M89" s="141" t="str">
+      <c r="M89" s="143" t="str">
         <f t="shared" si="5"/>
         <v>00 10 00 00</v>
       </c>
-      <c r="N89" s="141"/>
-      <c r="O89" s="141"/>
-      <c r="P89" s="141"/>
-      <c r="Q89" s="142"/>
+      <c r="N89" s="143"/>
+      <c r="O89" s="143"/>
+      <c r="P89" s="143"/>
+      <c r="Q89" s="144"/>
       <c r="R89" s="70"/>
       <c r="S89" s="51"/>
-      <c r="T89" s="143"/>
+      <c r="T89" s="123"/>
       <c r="U89" s="51"/>
       <c r="V89" s="51"/>
       <c r="W89" s="51"/>
@@ -9089,16 +9089,16 @@
     <row r="91" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A91" s="51"/>
       <c r="B91" s="64"/>
-      <c r="C91" s="125" t="s">
+      <c r="C91" s="148" t="s">
         <v>992</v>
       </c>
-      <c r="D91" s="125"/>
-      <c r="E91" s="125"/>
-      <c r="F91" s="125"/>
-      <c r="G91" s="125"/>
-      <c r="H91" s="125"/>
-      <c r="I91" s="125"/>
-      <c r="J91" s="125"/>
+      <c r="D91" s="148"/>
+      <c r="E91" s="148"/>
+      <c r="F91" s="148"/>
+      <c r="G91" s="148"/>
+      <c r="H91" s="148"/>
+      <c r="I91" s="148"/>
+      <c r="J91" s="148"/>
       <c r="K91" s="67"/>
       <c r="L91" s="54" t="s">
         <v>1</v>
@@ -9123,14 +9123,14 @@
     <row r="92" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A92" s="51"/>
       <c r="B92" s="64"/>
-      <c r="C92" s="125"/>
-      <c r="D92" s="125"/>
-      <c r="E92" s="125"/>
-      <c r="F92" s="125"/>
-      <c r="G92" s="125"/>
-      <c r="H92" s="125"/>
-      <c r="I92" s="125"/>
-      <c r="J92" s="125"/>
+      <c r="C92" s="148"/>
+      <c r="D92" s="148"/>
+      <c r="E92" s="148"/>
+      <c r="F92" s="148"/>
+      <c r="G92" s="148"/>
+      <c r="H92" s="148"/>
+      <c r="I92" s="148"/>
+      <c r="J92" s="148"/>
       <c r="K92" s="67"/>
       <c r="L92" s="117" t="str">
         <f>L32</f>
@@ -9186,23 +9186,23 @@
     <row r="94" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A94" s="51"/>
       <c r="B94" s="64"/>
-      <c r="C94" s="124" t="s">
+      <c r="C94" s="147" t="s">
         <v>991</v>
       </c>
-      <c r="D94" s="124"/>
-      <c r="E94" s="124"/>
-      <c r="F94" s="124"/>
-      <c r="G94" s="124"/>
-      <c r="H94" s="124"/>
-      <c r="I94" s="124"/>
-      <c r="J94" s="124"/>
-      <c r="K94" s="124"/>
-      <c r="L94" s="124"/>
-      <c r="M94" s="124"/>
-      <c r="N94" s="124"/>
-      <c r="O94" s="124"/>
-      <c r="P94" s="124"/>
-      <c r="Q94" s="124"/>
+      <c r="D94" s="147"/>
+      <c r="E94" s="147"/>
+      <c r="F94" s="147"/>
+      <c r="G94" s="147"/>
+      <c r="H94" s="147"/>
+      <c r="I94" s="147"/>
+      <c r="J94" s="147"/>
+      <c r="K94" s="147"/>
+      <c r="L94" s="147"/>
+      <c r="M94" s="147"/>
+      <c r="N94" s="147"/>
+      <c r="O94" s="147"/>
+      <c r="P94" s="147"/>
+      <c r="Q94" s="147"/>
       <c r="R94" s="70"/>
       <c r="S94" s="51"/>
       <c r="T94" s="101"/>
@@ -9218,24 +9218,24 @@
     <row r="95" spans="1:28" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="51"/>
       <c r="B95" s="64"/>
-      <c r="C95" s="123" t="str">
+      <c r="C95" s="146" t="str">
         <f>M32&amp;" "&amp;M33&amp;" "&amp;M34&amp;" "&amp;M35&amp;" "&amp;M36&amp;" "&amp;M37&amp;" "&amp;M38&amp;" "&amp;M39&amp;" "&amp;M40&amp;" "&amp;M41&amp;" "&amp;M42&amp;" "&amp;M43&amp;" "&amp;M44&amp;" "&amp;M45&amp;" "&amp;M46&amp;" "&amp;M47&amp;" "&amp;M48&amp;" "&amp;M49&amp;" "&amp;M50&amp;" "&amp;M51&amp;" "&amp;M52&amp;" "&amp;M53&amp;" "&amp;M54&amp;" "&amp;M55&amp;" "&amp;M56&amp;" "&amp;M57&amp;" "&amp;M58&amp;" "&amp;M59&amp;" "&amp;M60&amp;" "&amp;M61&amp;" "&amp;M62&amp;" "&amp;M63&amp;" "&amp;M64&amp;" "&amp;M65&amp;" "&amp;M66&amp;" "&amp;M67&amp;" "&amp;M68&amp;" "&amp;M69&amp;" "&amp;M70&amp;" "&amp;M71&amp;" "&amp;M72&amp;" "&amp;M73&amp;" "&amp;M74&amp;" "&amp;M75&amp;" "&amp;M76&amp;" "&amp;M77&amp;" "&amp;M78&amp;" "&amp;M79&amp;" "&amp;M80&amp;" "&amp;M81&amp;" "&amp;M82&amp;" "&amp;M83&amp;" "&amp;M84&amp;" "&amp;M85&amp;" "&amp;M86&amp;" "&amp;M87&amp;" "&amp;M88&amp;" "&amp;M89</f>
         <v>23 01 28 00 BD 00 20 01 D2 00 20 00 C4 00 30 00 CD 00 20 01 09 00 40 00 07 00 40 00 14 01 30 01 08 00 40 00 BA 01 28 01 91 01 28 01 D2 01 30 00 7C 01 20 01 AD 00 20 02 B4 00 28 02 3A 01 30 00 0E 01 28 02 1B 01 40 01 C8 00 30 01 F6 00 28 01 EB 00 28 02 44 01 28 01 AC 01 40 00 9A 01 30 00 9E 01 28 01 B9 01 20 01 EF 00 28 01 92 01 28 01 4E 01 28 01 89 01 28 02 83 01 30 02 54 01 20 01 0F 01 30 00 01 01 30 01 1A 01 28 00 85 01 28 00 81 00 28 02 FD 00 30 02 A2 00 28 01 DC 00 40 01 51 00 20 02 6E 01 30 02 64 01 20 02 84 01 20 02 15 01 20 02 10 01 30 02 D7 00 30 02 43 00 20 01 8F 00 40 01 4F 01 20 02 C2 01 20 00 1D 00 00 03 00 10 00 00 00 10 00 00 00 10 00 00 00 10 00 00 00 10 00 00 00 10 00 00</v>
       </c>
-      <c r="D95" s="123"/>
-      <c r="E95" s="123"/>
-      <c r="F95" s="123"/>
-      <c r="G95" s="123"/>
-      <c r="H95" s="123"/>
-      <c r="I95" s="123"/>
-      <c r="J95" s="123"/>
-      <c r="K95" s="123"/>
-      <c r="L95" s="123"/>
-      <c r="M95" s="123"/>
-      <c r="N95" s="123"/>
-      <c r="O95" s="123"/>
-      <c r="P95" s="123"/>
-      <c r="Q95" s="123"/>
+      <c r="D95" s="146"/>
+      <c r="E95" s="146"/>
+      <c r="F95" s="146"/>
+      <c r="G95" s="146"/>
+      <c r="H95" s="146"/>
+      <c r="I95" s="146"/>
+      <c r="J95" s="146"/>
+      <c r="K95" s="146"/>
+      <c r="L95" s="146"/>
+      <c r="M95" s="146"/>
+      <c r="N95" s="146"/>
+      <c r="O95" s="146"/>
+      <c r="P95" s="146"/>
+      <c r="Q95" s="146"/>
       <c r="R95" s="70"/>
       <c r="S95" s="51"/>
       <c r="T95" s="101"/>
@@ -11309,6 +11309,171 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="lUZj3iVy+ti12Q2f/ocgRKOxTSxhkDv+oRT4+1fE0U2P55/lL3+x4WX5QUG4IhZnIkfxdFXDX3DozZfxMulzuw==" saltValue="wEkNdTNOhASWaUOWJtgkww==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="189">
+    <mergeCell ref="C95:Q95"/>
+    <mergeCell ref="C94:Q94"/>
+    <mergeCell ref="C91:J92"/>
+    <mergeCell ref="B27:I28"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="K27:R28"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="J82:K82"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="J71:K71"/>
+    <mergeCell ref="J72:K72"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="J69:K69"/>
+    <mergeCell ref="J70:K70"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="J64:K64"/>
+    <mergeCell ref="J65:K65"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="M87:Q87"/>
+    <mergeCell ref="M88:Q88"/>
+    <mergeCell ref="M89:Q89"/>
+    <mergeCell ref="M81:Q81"/>
+    <mergeCell ref="M82:Q82"/>
+    <mergeCell ref="M83:Q83"/>
+    <mergeCell ref="M84:Q84"/>
+    <mergeCell ref="M85:Q85"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="M76:Q76"/>
+    <mergeCell ref="M77:Q77"/>
+    <mergeCell ref="M78:Q78"/>
+    <mergeCell ref="M79:Q79"/>
+    <mergeCell ref="M80:Q80"/>
+    <mergeCell ref="M71:Q71"/>
+    <mergeCell ref="M72:Q72"/>
+    <mergeCell ref="M73:Q73"/>
+    <mergeCell ref="M74:Q74"/>
+    <mergeCell ref="M75:Q75"/>
+    <mergeCell ref="M66:Q66"/>
+    <mergeCell ref="M63:Q63"/>
+    <mergeCell ref="M64:Q64"/>
+    <mergeCell ref="M65:Q65"/>
+    <mergeCell ref="M56:Q56"/>
+    <mergeCell ref="M57:Q57"/>
+    <mergeCell ref="M58:Q58"/>
+    <mergeCell ref="M59:Q59"/>
+    <mergeCell ref="M60:Q60"/>
+    <mergeCell ref="M86:Q86"/>
+    <mergeCell ref="M67:Q67"/>
+    <mergeCell ref="M68:Q68"/>
+    <mergeCell ref="M69:Q69"/>
+    <mergeCell ref="M70:Q70"/>
+    <mergeCell ref="M54:Q54"/>
+    <mergeCell ref="M55:Q55"/>
+    <mergeCell ref="M46:Q46"/>
+    <mergeCell ref="M47:Q47"/>
+    <mergeCell ref="M48:Q48"/>
+    <mergeCell ref="M49:Q49"/>
+    <mergeCell ref="M50:Q50"/>
+    <mergeCell ref="M61:Q61"/>
+    <mergeCell ref="M62:Q62"/>
+    <mergeCell ref="M45:Q45"/>
+    <mergeCell ref="M36:Q36"/>
+    <mergeCell ref="M37:Q37"/>
+    <mergeCell ref="M38:Q38"/>
+    <mergeCell ref="M39:Q39"/>
+    <mergeCell ref="M40:Q40"/>
+    <mergeCell ref="M51:Q51"/>
+    <mergeCell ref="M52:Q52"/>
+    <mergeCell ref="M53:Q53"/>
     <mergeCell ref="T84:T89"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="F37:G37"/>
@@ -11333,171 +11498,6 @@
     <mergeCell ref="M42:Q42"/>
     <mergeCell ref="M43:Q43"/>
     <mergeCell ref="M44:Q44"/>
-    <mergeCell ref="M45:Q45"/>
-    <mergeCell ref="M36:Q36"/>
-    <mergeCell ref="M37:Q37"/>
-    <mergeCell ref="M38:Q38"/>
-    <mergeCell ref="M39:Q39"/>
-    <mergeCell ref="M40:Q40"/>
-    <mergeCell ref="M51:Q51"/>
-    <mergeCell ref="M52:Q52"/>
-    <mergeCell ref="M53:Q53"/>
-    <mergeCell ref="M54:Q54"/>
-    <mergeCell ref="M55:Q55"/>
-    <mergeCell ref="M46:Q46"/>
-    <mergeCell ref="M47:Q47"/>
-    <mergeCell ref="M48:Q48"/>
-    <mergeCell ref="M49:Q49"/>
-    <mergeCell ref="M50:Q50"/>
-    <mergeCell ref="M61:Q61"/>
-    <mergeCell ref="M62:Q62"/>
-    <mergeCell ref="M63:Q63"/>
-    <mergeCell ref="M64:Q64"/>
-    <mergeCell ref="M65:Q65"/>
-    <mergeCell ref="M56:Q56"/>
-    <mergeCell ref="M57:Q57"/>
-    <mergeCell ref="M58:Q58"/>
-    <mergeCell ref="M59:Q59"/>
-    <mergeCell ref="M60:Q60"/>
-    <mergeCell ref="M86:Q86"/>
-    <mergeCell ref="M67:Q67"/>
-    <mergeCell ref="M68:Q68"/>
-    <mergeCell ref="M69:Q69"/>
-    <mergeCell ref="M70:Q70"/>
-    <mergeCell ref="M87:Q87"/>
-    <mergeCell ref="M88:Q88"/>
-    <mergeCell ref="M89:Q89"/>
-    <mergeCell ref="M81:Q81"/>
-    <mergeCell ref="M82:Q82"/>
-    <mergeCell ref="M83:Q83"/>
-    <mergeCell ref="M84:Q84"/>
-    <mergeCell ref="M85:Q85"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="M76:Q76"/>
-    <mergeCell ref="M77:Q77"/>
-    <mergeCell ref="M78:Q78"/>
-    <mergeCell ref="M79:Q79"/>
-    <mergeCell ref="M80:Q80"/>
-    <mergeCell ref="M71:Q71"/>
-    <mergeCell ref="M72:Q72"/>
-    <mergeCell ref="M73:Q73"/>
-    <mergeCell ref="M74:Q74"/>
-    <mergeCell ref="M75:Q75"/>
-    <mergeCell ref="M66:Q66"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="J62:K62"/>
-    <mergeCell ref="J63:K63"/>
-    <mergeCell ref="J64:K64"/>
-    <mergeCell ref="J65:K65"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="J71:K71"/>
-    <mergeCell ref="J72:K72"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="J69:K69"/>
-    <mergeCell ref="J70:K70"/>
-    <mergeCell ref="C95:Q95"/>
-    <mergeCell ref="C94:Q94"/>
-    <mergeCell ref="C91:J92"/>
-    <mergeCell ref="B27:I28"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="K27:R28"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="J88:K88"/>
-    <mergeCell ref="J89:K89"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="J82:K82"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J84:K84"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="J79:K79"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E24 I9:I24 M9:M24 Q9:Q24">
     <cfRule type="cellIs" dxfId="31" priority="19" operator="equal">
@@ -11600,7 +11600,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="I6 M6 L32:Q89 L92 C95" unlockedFormula="1"/>
+    <ignoredError sqref="M6 L32:Q89 L92 C95" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -11630,52 +11630,52 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="179" t="s">
+      <c r="B2" s="155" t="s">
         <v>985</v>
       </c>
-      <c r="C2" s="180"/>
-      <c r="D2" s="180"/>
-      <c r="E2" s="180"/>
-      <c r="F2" s="180"/>
-      <c r="G2" s="180"/>
-      <c r="H2" s="180"/>
-      <c r="I2" s="180"/>
-      <c r="J2" s="180"/>
-      <c r="K2" s="180"/>
-      <c r="L2" s="183" t="s">
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156"/>
+      <c r="L2" s="159" t="s">
         <v>570</v>
       </c>
-      <c r="M2" s="185" t="s">
+      <c r="M2" s="161" t="s">
         <v>1000</v>
       </c>
-      <c r="N2" s="185"/>
-      <c r="O2" s="185"/>
-      <c r="P2" s="185"/>
-      <c r="Q2" s="185"/>
-      <c r="R2" s="185"/>
-      <c r="S2" s="185"/>
-      <c r="T2" s="186"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161"/>
+      <c r="R2" s="161"/>
+      <c r="S2" s="161"/>
+      <c r="T2" s="162"/>
     </row>
     <row r="3" spans="2:20" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="181"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="184"/>
-      <c r="M3" s="187"/>
-      <c r="N3" s="187"/>
-      <c r="O3" s="187"/>
-      <c r="P3" s="187"/>
-      <c r="Q3" s="187"/>
-      <c r="R3" s="187"/>
-      <c r="S3" s="187"/>
-      <c r="T3" s="188"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="160"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="164"/>
     </row>
     <row r="4" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="28"/>
@@ -11728,20 +11728,20 @@
     <row r="6" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="28"/>
       <c r="C6" s="23"/>
-      <c r="D6" s="144" t="str">
+      <c r="D6" s="125" t="str">
         <f>VLOOKUP(E5,Lookups!A:B,2,0)</f>
         <v>Bulbasaur</v>
       </c>
-      <c r="E6" s="145"/>
+      <c r="E6" s="126"/>
       <c r="F6" s="18"/>
       <c r="G6" s="23"/>
-      <c r="H6" s="152" t="s">
+      <c r="H6" s="177" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="153"/>
-      <c r="J6" s="154"/>
+      <c r="I6" s="178"/>
+      <c r="J6" s="179"/>
       <c r="K6" s="112" t="str">
-        <f>(DEC2HEX(((E5-1)*8)+196908))</f>
+        <f>(DEC2HEX(((E5-1)*5)+196908))</f>
         <v>3012C</v>
       </c>
       <c r="L6" s="18"/>
@@ -11749,14 +11749,14 @@
       <c r="N6" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="O6" s="146" t="str">
+      <c r="O6" s="127" t="str">
         <f>IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(E16&amp;E15&amp;E14&amp;E13&amp;E12&amp;E11&amp;E10&amp;E9,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(E16&amp;E15&amp;E14&amp;E13&amp;E12&amp;E11&amp;E10&amp;E9,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(E16&amp;E15&amp;E14&amp;E13&amp;E12&amp;E11&amp;E10&amp;E9,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(E24&amp;E23&amp;E22&amp;E21&amp;E20&amp;E19&amp;E18&amp;E17,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(E24&amp;E23&amp;E22&amp;E21&amp;E20&amp;E19&amp;E18&amp;E17,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(E24&amp;E23&amp;E22&amp;E21&amp;E20&amp;E19&amp;E18&amp;E17,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(K16&amp;K15&amp;K14&amp;K13&amp;K12&amp;K11&amp;K10&amp;K9,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(K16&amp;K15&amp;K14&amp;K13&amp;K12&amp;K11&amp;K10&amp;K9,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(K16&amp;K15&amp;K14&amp;K13&amp;K12&amp;K11&amp;K10&amp;K9,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(K24&amp;K23&amp;K22&amp;K21&amp;K20&amp;K19&amp;K18&amp;K17,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(K24&amp;K23&amp;K22&amp;K21&amp;K20&amp;K19&amp;K18&amp;K17,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(K24&amp;K23&amp;K22&amp;K21&amp;K20&amp;K19&amp;K18&amp;K17,"N",0),"Y",1)))&amp;" "&amp;IF(LEN(BIN2HEX(SUBSTITUTE(SUBSTITUTE(O16&amp;O15&amp;O14&amp;O13&amp;O12&amp;O11&amp;O10&amp;O9,"N",0),"Y",1)))=1,"0"&amp;BIN2HEX(SUBSTITUTE(SUBSTITUTE(O16&amp;O15&amp;O14&amp;O13&amp;O12&amp;O11&amp;O10&amp;O9,"N",0),"Y",1)),BIN2HEX(SUBSTITUTE(SUBSTITUTE(O16&amp;O15&amp;O14&amp;O13&amp;O12&amp;O11&amp;O10&amp;O9,"N",0),"Y",1)))</f>
         <v>00 00 00 00 00</v>
       </c>
-      <c r="P6" s="146"/>
-      <c r="Q6" s="146"/>
-      <c r="R6" s="146"/>
-      <c r="S6" s="147"/>
+      <c r="P6" s="127"/>
+      <c r="Q6" s="127"/>
+      <c r="R6" s="127"/>
+      <c r="S6" s="128"/>
       <c r="T6" s="29"/>
     </row>
     <row r="7" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11795,11 +11795,11 @@
       <c r="G8" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="161" t="s">
+      <c r="H8" s="183" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="162"/>
-      <c r="J8" s="163"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="185"/>
       <c r="K8" s="88" t="s">
         <v>59</v>
       </c>
@@ -11835,12 +11835,12 @@
       <c r="G9" s="8">
         <v>17</v>
       </c>
-      <c r="H9" s="164" t="str">
+      <c r="H9" s="186" t="str">
         <f>VLOOKUP(G9,$C$31:$G$69,3,0)</f>
         <v>Helping Hand</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="J9" s="166"/>
+      <c r="I9" s="187"/>
+      <c r="J9" s="188"/>
       <c r="K9" s="102" t="s">
         <v>60</v>
       </c>
@@ -11877,12 +11877,12 @@
       <c r="G10" s="9">
         <v>18</v>
       </c>
-      <c r="H10" s="158" t="str">
+      <c r="H10" s="165" t="str">
         <f t="shared" ref="H10:H24" si="1">VLOOKUP(G10,$C$31:$G$69,3,0)</f>
         <v>Endeavor</v>
       </c>
-      <c r="I10" s="159"/>
-      <c r="J10" s="160"/>
+      <c r="I10" s="166"/>
+      <c r="J10" s="167"/>
       <c r="K10" s="103" t="s">
         <v>60</v>
       </c>
@@ -11919,12 +11919,12 @@
       <c r="G11" s="9">
         <v>19</v>
       </c>
-      <c r="H11" s="158" t="str">
+      <c r="H11" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Outrage</v>
       </c>
-      <c r="I11" s="159"/>
-      <c r="J11" s="160"/>
+      <c r="I11" s="166"/>
+      <c r="J11" s="167"/>
       <c r="K11" s="103" t="s">
         <v>60</v>
       </c>
@@ -11961,12 +11961,12 @@
       <c r="G12" s="9">
         <v>20</v>
       </c>
-      <c r="H12" s="158" t="str">
+      <c r="H12" s="165" t="str">
         <f t="shared" si="1"/>
         <v>AncientPower</v>
       </c>
-      <c r="I12" s="159"/>
-      <c r="J12" s="160"/>
+      <c r="I12" s="166"/>
+      <c r="J12" s="167"/>
       <c r="K12" s="103" t="s">
         <v>60</v>
       </c>
@@ -12003,12 +12003,12 @@
       <c r="G13" s="9">
         <v>21</v>
       </c>
-      <c r="H13" s="158" t="str">
+      <c r="H13" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Synthesis</v>
       </c>
-      <c r="I13" s="159"/>
-      <c r="J13" s="160"/>
+      <c r="I13" s="166"/>
+      <c r="J13" s="167"/>
       <c r="K13" s="103" t="s">
         <v>60</v>
       </c>
@@ -12045,12 +12045,12 @@
       <c r="G14" s="9">
         <v>22</v>
       </c>
-      <c r="H14" s="158" t="str">
+      <c r="H14" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Signal Beam</v>
       </c>
-      <c r="I14" s="159"/>
-      <c r="J14" s="160"/>
+      <c r="I14" s="166"/>
+      <c r="J14" s="167"/>
       <c r="K14" s="103" t="s">
         <v>60</v>
       </c>
@@ -12087,12 +12087,12 @@
       <c r="G15" s="9">
         <v>23</v>
       </c>
-      <c r="H15" s="158" t="str">
+      <c r="H15" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Zen Headbutt</v>
       </c>
-      <c r="I15" s="159"/>
-      <c r="J15" s="160"/>
+      <c r="I15" s="166"/>
+      <c r="J15" s="167"/>
       <c r="K15" s="103" t="s">
         <v>60</v>
       </c>
@@ -12122,12 +12122,12 @@
       <c r="G16" s="9">
         <v>24</v>
       </c>
-      <c r="H16" s="158" t="str">
+      <c r="H16" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Vacuum Wave</v>
       </c>
-      <c r="I16" s="159"/>
-      <c r="J16" s="160"/>
+      <c r="I16" s="166"/>
+      <c r="J16" s="167"/>
       <c r="K16" s="103" t="s">
         <v>60</v>
       </c>
@@ -12157,12 +12157,12 @@
       <c r="G17" s="9">
         <v>25</v>
       </c>
-      <c r="H17" s="158" t="str">
+      <c r="H17" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Earth Power</v>
       </c>
-      <c r="I17" s="159"/>
-      <c r="J17" s="160"/>
+      <c r="I17" s="166"/>
+      <c r="J17" s="167"/>
       <c r="K17" s="103" t="s">
         <v>60</v>
       </c>
@@ -12192,12 +12192,12 @@
       <c r="G18" s="9">
         <v>26</v>
       </c>
-      <c r="H18" s="158" t="str">
+      <c r="H18" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Gunk Shot</v>
       </c>
-      <c r="I18" s="159"/>
-      <c r="J18" s="160"/>
+      <c r="I18" s="166"/>
+      <c r="J18" s="167"/>
       <c r="K18" s="103" t="s">
         <v>60</v>
       </c>
@@ -12227,12 +12227,12 @@
       <c r="G19" s="9">
         <v>27</v>
       </c>
-      <c r="H19" s="158" t="str">
+      <c r="H19" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Twister</v>
       </c>
-      <c r="I19" s="159"/>
-      <c r="J19" s="160"/>
+      <c r="I19" s="166"/>
+      <c r="J19" s="167"/>
       <c r="K19" s="103" t="s">
         <v>60</v>
       </c>
@@ -12262,12 +12262,12 @@
       <c r="G20" s="9">
         <v>28</v>
       </c>
-      <c r="H20" s="158" t="str">
+      <c r="H20" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Seed Bomb</v>
       </c>
-      <c r="I20" s="159"/>
-      <c r="J20" s="160"/>
+      <c r="I20" s="166"/>
+      <c r="J20" s="167"/>
       <c r="K20" s="103" t="s">
         <v>60</v>
       </c>
@@ -12297,12 +12297,12 @@
       <c r="G21" s="9">
         <v>29</v>
       </c>
-      <c r="H21" s="158" t="str">
+      <c r="H21" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Iron Defense</v>
       </c>
-      <c r="I21" s="159"/>
-      <c r="J21" s="160"/>
+      <c r="I21" s="166"/>
+      <c r="J21" s="167"/>
       <c r="K21" s="103" t="s">
         <v>60</v>
       </c>
@@ -12332,12 +12332,12 @@
       <c r="G22" s="9">
         <v>30</v>
       </c>
-      <c r="H22" s="158" t="str">
+      <c r="H22" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Magnet Rise</v>
       </c>
-      <c r="I22" s="159"/>
-      <c r="J22" s="160"/>
+      <c r="I22" s="166"/>
+      <c r="J22" s="167"/>
       <c r="K22" s="103" t="s">
         <v>60</v>
       </c>
@@ -12367,12 +12367,12 @@
       <c r="G23" s="9">
         <v>31</v>
       </c>
-      <c r="H23" s="158" t="str">
+      <c r="H23" s="165" t="str">
         <f t="shared" si="1"/>
         <v>Last Resort</v>
       </c>
-      <c r="I23" s="159"/>
-      <c r="J23" s="160"/>
+      <c r="I23" s="166"/>
+      <c r="J23" s="167"/>
       <c r="K23" s="103" t="s">
         <v>60</v>
       </c>
@@ -12402,12 +12402,12 @@
       <c r="G24" s="10">
         <v>32</v>
       </c>
-      <c r="H24" s="149" t="str">
+      <c r="H24" s="174" t="str">
         <f t="shared" si="1"/>
         <v>Bounce</v>
       </c>
-      <c r="I24" s="150"/>
-      <c r="J24" s="151"/>
+      <c r="I24" s="175"/>
+      <c r="J24" s="176"/>
       <c r="K24" s="104" t="s">
         <v>60</v>
       </c>
@@ -12445,31 +12445,31 @@
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="51"/>
-      <c r="B27" s="179" t="s">
+      <c r="B27" s="155" t="s">
         <v>985</v>
       </c>
-      <c r="C27" s="180"/>
-      <c r="D27" s="180"/>
-      <c r="E27" s="180"/>
-      <c r="F27" s="180"/>
-      <c r="G27" s="180"/>
-      <c r="H27" s="180"/>
-      <c r="I27" s="180"/>
-      <c r="J27" s="180"/>
-      <c r="K27" s="180"/>
-      <c r="L27" s="183" t="s">
+      <c r="C27" s="156"/>
+      <c r="D27" s="156"/>
+      <c r="E27" s="156"/>
+      <c r="F27" s="156"/>
+      <c r="G27" s="156"/>
+      <c r="H27" s="156"/>
+      <c r="I27" s="156"/>
+      <c r="J27" s="156"/>
+      <c r="K27" s="156"/>
+      <c r="L27" s="159" t="s">
         <v>570</v>
       </c>
-      <c r="M27" s="185" t="s">
+      <c r="M27" s="161" t="s">
         <v>999</v>
       </c>
-      <c r="N27" s="185"/>
-      <c r="O27" s="185"/>
-      <c r="P27" s="185"/>
-      <c r="Q27" s="185"/>
-      <c r="R27" s="185"/>
-      <c r="S27" s="185"/>
-      <c r="T27" s="186"/>
+      <c r="N27" s="161"/>
+      <c r="O27" s="161"/>
+      <c r="P27" s="161"/>
+      <c r="Q27" s="161"/>
+      <c r="R27" s="161"/>
+      <c r="S27" s="161"/>
+      <c r="T27" s="162"/>
       <c r="U27" s="51"/>
       <c r="V27" s="51"/>
       <c r="W27" s="51"/>
@@ -12483,25 +12483,25 @@
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="51"/>
-      <c r="B28" s="181"/>
-      <c r="C28" s="182"/>
-      <c r="D28" s="182"/>
-      <c r="E28" s="182"/>
-      <c r="F28" s="182"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="182"/>
-      <c r="I28" s="182"/>
-      <c r="J28" s="182"/>
-      <c r="K28" s="182"/>
-      <c r="L28" s="184"/>
-      <c r="M28" s="187"/>
-      <c r="N28" s="187"/>
-      <c r="O28" s="187"/>
-      <c r="P28" s="187"/>
-      <c r="Q28" s="187"/>
-      <c r="R28" s="187"/>
-      <c r="S28" s="187"/>
-      <c r="T28" s="188"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="158"/>
+      <c r="D28" s="158"/>
+      <c r="E28" s="158"/>
+      <c r="F28" s="158"/>
+      <c r="G28" s="158"/>
+      <c r="H28" s="158"/>
+      <c r="I28" s="158"/>
+      <c r="J28" s="158"/>
+      <c r="K28" s="158"/>
+      <c r="L28" s="160"/>
+      <c r="M28" s="163"/>
+      <c r="N28" s="163"/>
+      <c r="O28" s="163"/>
+      <c r="P28" s="163"/>
+      <c r="Q28" s="163"/>
+      <c r="R28" s="163"/>
+      <c r="S28" s="163"/>
+      <c r="T28" s="164"/>
       <c r="U28" s="51"/>
       <c r="V28" s="51"/>
       <c r="W28" s="51"/>
@@ -12553,12 +12553,12 @@
       <c r="E30" s="80"/>
       <c r="F30" s="80"/>
       <c r="G30" s="23"/>
-      <c r="H30" s="155" t="s">
+      <c r="H30" s="180" t="s">
         <v>998</v>
       </c>
-      <c r="I30" s="156"/>
-      <c r="J30" s="156"/>
-      <c r="K30" s="157"/>
+      <c r="I30" s="181"/>
+      <c r="J30" s="181"/>
+      <c r="K30" s="182"/>
       <c r="L30" s="80"/>
       <c r="M30" s="23"/>
       <c r="N30" s="94" t="s">
@@ -12590,11 +12590,11 @@
       <c r="D31" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="E31" s="176" t="s">
+      <c r="E31" s="149" t="s">
         <v>3</v>
       </c>
-      <c r="F31" s="177"/>
-      <c r="G31" s="178"/>
+      <c r="F31" s="150"/>
+      <c r="G31" s="151"/>
       <c r="H31" s="83" t="s">
         <v>996</v>
       </c>
@@ -12607,20 +12607,20 @@
       <c r="K31" s="83" t="s">
         <v>994</v>
       </c>
-      <c r="L31" s="174" t="s">
+      <c r="L31" s="168" t="s">
         <v>990</v>
       </c>
-      <c r="M31" s="174"/>
+      <c r="M31" s="168"/>
       <c r="N31" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="O31" s="174" t="s">
+      <c r="O31" s="168" t="s">
         <v>991</v>
       </c>
-      <c r="P31" s="174"/>
-      <c r="Q31" s="174"/>
-      <c r="R31" s="174"/>
-      <c r="S31" s="175"/>
+      <c r="P31" s="168"/>
+      <c r="Q31" s="168"/>
+      <c r="R31" s="168"/>
+      <c r="S31" s="169"/>
       <c r="T31" s="75"/>
       <c r="U31" s="51"/>
       <c r="V31" s="51"/>
@@ -12642,12 +12642,12 @@
       <c r="D32" s="110">
         <v>291</v>
       </c>
-      <c r="E32" s="167" t="str">
+      <c r="E32" s="152" t="str">
         <f>VLOOKUP(D32,Lookups!$D:$E,2,0)</f>
         <v>Dive</v>
       </c>
-      <c r="F32" s="168"/>
-      <c r="G32" s="169"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="154"/>
       <c r="H32" s="113">
         <v>2</v>
       </c>
@@ -12660,22 +12660,22 @@
       <c r="K32" s="116">
         <v>0</v>
       </c>
-      <c r="L32" s="136">
+      <c r="L32" s="124">
         <v>0</v>
       </c>
-      <c r="M32" s="136"/>
+      <c r="M32" s="124"/>
       <c r="N32" s="117" t="str">
         <f>DEC2HEX(196452+(($C32-1)*12))</f>
         <v>2FF64</v>
       </c>
-      <c r="O32" s="139" t="str">
+      <c r="O32" s="141" t="str">
         <f t="shared" ref="O32:O36" si="3">IF(LEN(DEC2HEX($D32))=1,"0"&amp;DEC2HEX($D32)&amp;" 00",IF(LEN(DEC2HEX($D32))=2,DEC2HEX($D32)&amp;" 00",IF(LEN(DEC2HEX($D32))=3,RIGHT(DEC2HEX($D32),2)&amp;" 0"&amp;LEFT(DEC2HEX($D32),1),IF(LEN(DEC2HEX($D32))=4,RIGHT(DEC2HEX($D32),2)&amp;" "&amp;LEFT(DEC2HEX($D32),2),"Error - Move ID too high"))))&amp;" "&amp;IF(LEN(DEC2HEX(H32))=1,"0"&amp;DEC2HEX(H32),DEC2HEX(H32))&amp;" "&amp;IF(LEN(DEC2HEX(I32))=1,"0"&amp;DEC2HEX(I32),DEC2HEX(I32))&amp;" "&amp;IF(LEN(DEC2HEX(J32))=1,"0"&amp;DEC2HEX(J32),DEC2HEX(J32))&amp;" "&amp;IF(LEN(DEC2HEX(K32))=1,"0"&amp;DEC2HEX(K32),DEC2HEX(K32))&amp;" 00 00 "&amp;IF(LEN(DEC2HEX(L32))=1,"0"&amp;DEC2HEX(L32),DEC2HEX(L32))&amp;" 00 00 00"</f>
         <v>23 01 02 04 02 00 00 00 00 00 00 00</v>
       </c>
-      <c r="P32" s="139"/>
-      <c r="Q32" s="139"/>
-      <c r="R32" s="139"/>
-      <c r="S32" s="140"/>
+      <c r="P32" s="141"/>
+      <c r="Q32" s="141"/>
+      <c r="R32" s="141"/>
+      <c r="S32" s="142"/>
       <c r="T32" s="76"/>
       <c r="U32" s="51"/>
       <c r="V32" s="51"/>
@@ -12697,12 +12697,12 @@
       <c r="D33" s="110">
         <v>189</v>
       </c>
-      <c r="E33" s="167" t="str">
+      <c r="E33" s="152" t="str">
         <f>VLOOKUP(D33,Lookups!$D:$E,2,0)</f>
         <v>Mud-Slap</v>
       </c>
-      <c r="F33" s="168"/>
-      <c r="G33" s="169"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="154"/>
       <c r="H33" s="113">
         <v>4</v>
       </c>
@@ -12715,22 +12715,22 @@
       <c r="K33" s="116">
         <v>0</v>
       </c>
-      <c r="L33" s="136">
+      <c r="L33" s="124">
         <v>1</v>
       </c>
-      <c r="M33" s="136"/>
+      <c r="M33" s="124"/>
       <c r="N33" s="117" t="str">
         <f t="shared" ref="N33:N69" si="4">DEC2HEX(196452+(($C33-1)*12))</f>
         <v>2FF70</v>
       </c>
-      <c r="O33" s="139" t="str">
+      <c r="O33" s="141" t="str">
         <f t="shared" si="3"/>
         <v>BD 00 04 04 00 00 00 00 01 00 00 00</v>
       </c>
-      <c r="P33" s="139"/>
-      <c r="Q33" s="139"/>
-      <c r="R33" s="139"/>
-      <c r="S33" s="140"/>
+      <c r="P33" s="141"/>
+      <c r="Q33" s="141"/>
+      <c r="R33" s="141"/>
+      <c r="S33" s="142"/>
       <c r="T33" s="76"/>
       <c r="U33" s="51"/>
       <c r="V33" s="51"/>
@@ -12752,12 +12752,12 @@
       <c r="D34" s="110">
         <v>210</v>
       </c>
-      <c r="E34" s="167" t="str">
+      <c r="E34" s="152" t="str">
         <f>VLOOKUP(D34,Lookups!$D:$E,2,0)</f>
         <v>Fury Cutter</v>
       </c>
-      <c r="F34" s="168"/>
-      <c r="G34" s="169"/>
+      <c r="F34" s="153"/>
+      <c r="G34" s="154"/>
       <c r="H34" s="113">
         <v>0</v>
       </c>
@@ -12770,22 +12770,22 @@
       <c r="K34" s="116">
         <v>0</v>
       </c>
-      <c r="L34" s="136">
+      <c r="L34" s="124">
         <v>0</v>
       </c>
-      <c r="M34" s="136"/>
+      <c r="M34" s="124"/>
       <c r="N34" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FF7C</v>
       </c>
-      <c r="O34" s="139" t="str">
+      <c r="O34" s="141" t="str">
         <f t="shared" si="3"/>
         <v>D2 00 00 08 00 00 00 00 00 00 00 00</v>
       </c>
-      <c r="P34" s="139"/>
-      <c r="Q34" s="139"/>
-      <c r="R34" s="139"/>
-      <c r="S34" s="140"/>
+      <c r="P34" s="141"/>
+      <c r="Q34" s="141"/>
+      <c r="R34" s="141"/>
+      <c r="S34" s="142"/>
       <c r="T34" s="76"/>
       <c r="U34" s="51"/>
       <c r="V34" s="51"/>
@@ -12807,12 +12807,12 @@
       <c r="D35" s="110">
         <v>196</v>
       </c>
-      <c r="E35" s="167" t="str">
+      <c r="E35" s="152" t="str">
         <f>VLOOKUP(D35,Lookups!$D:$E,2,0)</f>
         <v>Icy Wind</v>
       </c>
-      <c r="F35" s="168"/>
-      <c r="G35" s="169"/>
+      <c r="F35" s="153"/>
+      <c r="G35" s="154"/>
       <c r="H35" s="113">
         <v>0</v>
       </c>
@@ -12825,22 +12825,22 @@
       <c r="K35" s="116">
         <v>2</v>
       </c>
-      <c r="L35" s="136">
+      <c r="L35" s="124">
         <v>0</v>
       </c>
-      <c r="M35" s="136"/>
+      <c r="M35" s="124"/>
       <c r="N35" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FF88</v>
       </c>
-      <c r="O35" s="139" t="str">
+      <c r="O35" s="141" t="str">
         <f t="shared" si="3"/>
         <v>C4 00 00 06 00 02 00 00 00 00 00 00</v>
       </c>
-      <c r="P35" s="139"/>
-      <c r="Q35" s="139"/>
-      <c r="R35" s="139"/>
-      <c r="S35" s="140"/>
+      <c r="P35" s="141"/>
+      <c r="Q35" s="141"/>
+      <c r="R35" s="141"/>
+      <c r="S35" s="142"/>
       <c r="T35" s="76"/>
       <c r="U35" s="51"/>
       <c r="V35" s="51"/>
@@ -12862,12 +12862,12 @@
       <c r="D36" s="110">
         <v>205</v>
       </c>
-      <c r="E36" s="167" t="str">
+      <c r="E36" s="152" t="str">
         <f>VLOOKUP(D36,Lookups!$D:$E,2,0)</f>
         <v>Rollout</v>
       </c>
-      <c r="F36" s="168"/>
-      <c r="G36" s="169"/>
+      <c r="F36" s="153"/>
+      <c r="G36" s="154"/>
       <c r="H36" s="113">
         <v>4</v>
       </c>
@@ -12880,22 +12880,22 @@
       <c r="K36" s="116">
         <v>2</v>
       </c>
-      <c r="L36" s="136">
+      <c r="L36" s="124">
         <v>1</v>
       </c>
-      <c r="M36" s="136"/>
+      <c r="M36" s="124"/>
       <c r="N36" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FF94</v>
       </c>
-      <c r="O36" s="139" t="str">
+      <c r="O36" s="141" t="str">
         <f t="shared" si="3"/>
         <v>CD 00 04 02 00 02 00 00 01 00 00 00</v>
       </c>
-      <c r="P36" s="139"/>
-      <c r="Q36" s="139"/>
-      <c r="R36" s="139"/>
-      <c r="S36" s="140"/>
+      <c r="P36" s="141"/>
+      <c r="Q36" s="141"/>
+      <c r="R36" s="141"/>
+      <c r="S36" s="142"/>
       <c r="T36" s="76"/>
       <c r="U36" s="51"/>
       <c r="V36" s="51"/>
@@ -12917,12 +12917,12 @@
       <c r="D37" s="110">
         <v>9</v>
       </c>
-      <c r="E37" s="167" t="str">
+      <c r="E37" s="152" t="str">
         <f>VLOOKUP(D37,Lookups!$D:$E,2,0)</f>
         <v>ThunderPunch</v>
       </c>
-      <c r="F37" s="168"/>
-      <c r="G37" s="169"/>
+      <c r="F37" s="153"/>
+      <c r="G37" s="154"/>
       <c r="H37" s="113">
         <v>2</v>
       </c>
@@ -12935,22 +12935,22 @@
       <c r="K37" s="116">
         <v>0</v>
       </c>
-      <c r="L37" s="136">
+      <c r="L37" s="124">
         <v>0</v>
       </c>
-      <c r="M37" s="136"/>
+      <c r="M37" s="124"/>
       <c r="N37" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FFA0</v>
       </c>
-      <c r="O37" s="139" t="str">
+      <c r="O37" s="141" t="str">
         <f>IF(LEN(DEC2HEX($D37))=1,"0"&amp;DEC2HEX($D37)&amp;" 00",IF(LEN(DEC2HEX($D37))=2,DEC2HEX($D37)&amp;" 00",IF(LEN(DEC2HEX($D37))=3,RIGHT(DEC2HEX($D37),2)&amp;" 0"&amp;LEFT(DEC2HEX($D37),1),IF(LEN(DEC2HEX($D37))=4,RIGHT(DEC2HEX($D37),2)&amp;" "&amp;LEFT(DEC2HEX($D37),2),"Error - Move ID too high"))))&amp;" "&amp;IF(LEN(DEC2HEX(H37))=1,"0"&amp;DEC2HEX(H37),DEC2HEX(H37))&amp;" "&amp;IF(LEN(DEC2HEX(I37))=1,"0"&amp;DEC2HEX(I37),DEC2HEX(I37))&amp;" "&amp;IF(LEN(DEC2HEX(J37))=1,"0"&amp;DEC2HEX(J37),DEC2HEX(J37))&amp;" "&amp;IF(LEN(DEC2HEX(K37))=1,"0"&amp;DEC2HEX(K37),DEC2HEX(K37))&amp;" 00 00 "&amp;IF(LEN(DEC2HEX(L37))=1,"0"&amp;DEC2HEX(L37),DEC2HEX(L37))&amp;" 00 00 00"</f>
         <v>09 00 02 06 00 00 00 00 00 00 00 00</v>
       </c>
-      <c r="P37" s="139"/>
-      <c r="Q37" s="139"/>
-      <c r="R37" s="139"/>
-      <c r="S37" s="140"/>
+      <c r="P37" s="141"/>
+      <c r="Q37" s="141"/>
+      <c r="R37" s="141"/>
+      <c r="S37" s="142"/>
       <c r="T37" s="76"/>
       <c r="U37" s="51"/>
       <c r="V37" s="51"/>
@@ -12972,12 +12972,12 @@
       <c r="D38" s="110">
         <v>7</v>
       </c>
-      <c r="E38" s="167" t="str">
+      <c r="E38" s="152" t="str">
         <f>VLOOKUP(D38,Lookups!$D:$E,2,0)</f>
         <v>Fire Punch</v>
       </c>
-      <c r="F38" s="168"/>
-      <c r="G38" s="169"/>
+      <c r="F38" s="153"/>
+      <c r="G38" s="154"/>
       <c r="H38" s="113">
         <v>2</v>
       </c>
@@ -12990,22 +12990,22 @@
       <c r="K38" s="116">
         <v>0</v>
       </c>
-      <c r="L38" s="136">
+      <c r="L38" s="124">
         <v>0</v>
       </c>
-      <c r="M38" s="136"/>
+      <c r="M38" s="124"/>
       <c r="N38" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FFAC</v>
       </c>
-      <c r="O38" s="139" t="str">
+      <c r="O38" s="141" t="str">
         <f t="shared" ref="O38:O69" si="5">IF(LEN(DEC2HEX($D38))=1,"0"&amp;DEC2HEX($D38)&amp;" 00",IF(LEN(DEC2HEX($D38))=2,DEC2HEX($D38)&amp;" 00",IF(LEN(DEC2HEX($D38))=3,RIGHT(DEC2HEX($D38),2)&amp;" 0"&amp;LEFT(DEC2HEX($D38),1),IF(LEN(DEC2HEX($D38))=4,RIGHT(DEC2HEX($D38),2)&amp;" "&amp;LEFT(DEC2HEX($D38),2),"Error - Move ID too high"))))&amp;" "&amp;IF(LEN(DEC2HEX(H38))=1,"0"&amp;DEC2HEX(H38),DEC2HEX(H38))&amp;" "&amp;IF(LEN(DEC2HEX(I38))=1,"0"&amp;DEC2HEX(I38),DEC2HEX(I38))&amp;" "&amp;IF(LEN(DEC2HEX(J38))=1,"0"&amp;DEC2HEX(J38),DEC2HEX(J38))&amp;" "&amp;IF(LEN(DEC2HEX(K38))=1,"0"&amp;DEC2HEX(K38),DEC2HEX(K38))&amp;" 00 00 "&amp;IF(LEN(DEC2HEX(L38))=1,"0"&amp;DEC2HEX(L38),DEC2HEX(L38))&amp;" 00 00 00"</f>
         <v>07 00 02 06 00 00 00 00 00 00 00 00</v>
       </c>
-      <c r="P38" s="139"/>
-      <c r="Q38" s="139"/>
-      <c r="R38" s="139"/>
-      <c r="S38" s="140"/>
+      <c r="P38" s="141"/>
+      <c r="Q38" s="141"/>
+      <c r="R38" s="141"/>
+      <c r="S38" s="142"/>
       <c r="T38" s="76"/>
       <c r="U38" s="51"/>
       <c r="V38" s="51"/>
@@ -13027,12 +13027,12 @@
       <c r="D39" s="110">
         <v>276</v>
       </c>
-      <c r="E39" s="167" t="str">
+      <c r="E39" s="152" t="str">
         <f>VLOOKUP(D39,Lookups!$D:$E,2,0)</f>
         <v>Superpower</v>
       </c>
-      <c r="F39" s="168"/>
-      <c r="G39" s="169"/>
+      <c r="F39" s="153"/>
+      <c r="G39" s="154"/>
       <c r="H39" s="113">
         <v>8</v>
       </c>
@@ -13045,22 +13045,22 @@
       <c r="K39" s="116">
         <v>0</v>
       </c>
-      <c r="L39" s="136">
+      <c r="L39" s="124">
         <v>1</v>
       </c>
-      <c r="M39" s="136"/>
+      <c r="M39" s="124"/>
       <c r="N39" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FFB8</v>
       </c>
-      <c r="O39" s="139" t="str">
+      <c r="O39" s="141" t="str">
         <f t="shared" si="5"/>
         <v>14 01 08 00 00 00 00 00 01 00 00 00</v>
       </c>
-      <c r="P39" s="139"/>
-      <c r="Q39" s="139"/>
-      <c r="R39" s="139"/>
-      <c r="S39" s="140"/>
+      <c r="P39" s="141"/>
+      <c r="Q39" s="141"/>
+      <c r="R39" s="141"/>
+      <c r="S39" s="142"/>
       <c r="T39" s="76"/>
       <c r="U39" s="51"/>
       <c r="V39" s="51"/>
@@ -13082,12 +13082,12 @@
       <c r="D40" s="110">
         <v>8</v>
       </c>
-      <c r="E40" s="167" t="str">
+      <c r="E40" s="152" t="str">
         <f>VLOOKUP(D40,Lookups!$D:$E,2,0)</f>
         <v>Ice Punch</v>
       </c>
-      <c r="F40" s="168"/>
-      <c r="G40" s="169"/>
+      <c r="F40" s="153"/>
+      <c r="G40" s="154"/>
       <c r="H40" s="113">
         <v>2</v>
       </c>
@@ -13100,22 +13100,22 @@
       <c r="K40" s="116">
         <v>0</v>
       </c>
-      <c r="L40" s="136">
+      <c r="L40" s="124">
         <v>0</v>
       </c>
-      <c r="M40" s="136"/>
+      <c r="M40" s="124"/>
       <c r="N40" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FFC4</v>
       </c>
-      <c r="O40" s="139" t="str">
+      <c r="O40" s="141" t="str">
         <f t="shared" si="5"/>
         <v>08 00 02 06 00 00 00 00 00 00 00 00</v>
       </c>
-      <c r="P40" s="139"/>
-      <c r="Q40" s="139"/>
-      <c r="R40" s="139"/>
-      <c r="S40" s="140"/>
+      <c r="P40" s="141"/>
+      <c r="Q40" s="141"/>
+      <c r="R40" s="141"/>
+      <c r="S40" s="142"/>
       <c r="T40" s="76"/>
       <c r="U40" s="51"/>
       <c r="V40" s="51"/>
@@ -13137,12 +13137,12 @@
       <c r="D41" s="110">
         <v>442</v>
       </c>
-      <c r="E41" s="167" t="str">
+      <c r="E41" s="152" t="str">
         <f>VLOOKUP(D41,Lookups!$D:$E,2,0)</f>
         <v>Iron Head</v>
       </c>
-      <c r="F41" s="168"/>
-      <c r="G41" s="169"/>
+      <c r="F41" s="153"/>
+      <c r="G41" s="154"/>
       <c r="H41" s="113">
         <v>6</v>
       </c>
@@ -13155,22 +13155,22 @@
       <c r="K41" s="116">
         <v>0</v>
       </c>
-      <c r="L41" s="136">
+      <c r="L41" s="124">
         <v>1</v>
       </c>
-      <c r="M41" s="136"/>
+      <c r="M41" s="124"/>
       <c r="N41" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FFD0</v>
       </c>
-      <c r="O41" s="139" t="str">
+      <c r="O41" s="141" t="str">
         <f t="shared" si="5"/>
         <v>BA 01 06 00 02 00 00 00 01 00 00 00</v>
       </c>
-      <c r="P41" s="139"/>
-      <c r="Q41" s="139"/>
-      <c r="R41" s="139"/>
-      <c r="S41" s="140"/>
+      <c r="P41" s="141"/>
+      <c r="Q41" s="141"/>
+      <c r="R41" s="141"/>
+      <c r="S41" s="142"/>
       <c r="T41" s="76"/>
       <c r="U41" s="51"/>
       <c r="V41" s="51"/>
@@ -13192,12 +13192,12 @@
       <c r="D42" s="110">
         <v>401</v>
       </c>
-      <c r="E42" s="167" t="str">
+      <c r="E42" s="152" t="str">
         <f>VLOOKUP(D42,Lookups!$D:$E,2,0)</f>
         <v>Aqua Tail</v>
       </c>
-      <c r="F42" s="168"/>
-      <c r="G42" s="169"/>
+      <c r="F42" s="153"/>
+      <c r="G42" s="154"/>
       <c r="H42" s="113">
         <v>6</v>
       </c>
@@ -13210,22 +13210,22 @@
       <c r="K42" s="116">
         <v>2</v>
       </c>
-      <c r="L42" s="136">
+      <c r="L42" s="124">
         <v>1</v>
       </c>
-      <c r="M42" s="136"/>
+      <c r="M42" s="124"/>
       <c r="N42" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FFDC</v>
       </c>
-      <c r="O42" s="139" t="str">
+      <c r="O42" s="141" t="str">
         <f t="shared" si="5"/>
         <v>91 01 06 00 00 02 00 00 01 00 00 00</v>
       </c>
-      <c r="P42" s="139"/>
-      <c r="Q42" s="139"/>
-      <c r="R42" s="139"/>
-      <c r="S42" s="140"/>
+      <c r="P42" s="141"/>
+      <c r="Q42" s="141"/>
+      <c r="R42" s="141"/>
+      <c r="S42" s="142"/>
       <c r="T42" s="76"/>
       <c r="U42" s="51"/>
       <c r="V42" s="51"/>
@@ -13247,12 +13247,12 @@
       <c r="D43" s="110">
         <v>466</v>
       </c>
-      <c r="E43" s="167" t="str">
+      <c r="E43" s="152" t="str">
         <f>VLOOKUP(D43,Lookups!$D:$E,2,0)</f>
         <v>Ominous Wind</v>
       </c>
-      <c r="F43" s="168"/>
-      <c r="G43" s="169"/>
+      <c r="F43" s="153"/>
+      <c r="G43" s="154"/>
       <c r="H43" s="113">
         <v>0</v>
       </c>
@@ -13265,22 +13265,22 @@
       <c r="K43" s="116">
         <v>2</v>
       </c>
-      <c r="L43" s="136">
+      <c r="L43" s="124">
         <v>0</v>
       </c>
-      <c r="M43" s="136"/>
+      <c r="M43" s="124"/>
       <c r="N43" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FFE8</v>
       </c>
-      <c r="O43" s="139" t="str">
+      <c r="O43" s="141" t="str">
         <f t="shared" si="5"/>
         <v>D2 01 00 06 00 02 00 00 00 00 00 00</v>
       </c>
-      <c r="P43" s="139"/>
-      <c r="Q43" s="139"/>
-      <c r="R43" s="139"/>
-      <c r="S43" s="140"/>
+      <c r="P43" s="141"/>
+      <c r="Q43" s="141"/>
+      <c r="R43" s="141"/>
+      <c r="S43" s="142"/>
       <c r="T43" s="76"/>
       <c r="U43" s="51"/>
       <c r="V43" s="51"/>
@@ -13302,12 +13302,12 @@
       <c r="D44" s="110">
         <v>380</v>
       </c>
-      <c r="E44" s="167" t="str">
+      <c r="E44" s="152" t="str">
         <f>VLOOKUP(D44,Lookups!$D:$E,2,0)</f>
         <v>Gastro Acid</v>
       </c>
-      <c r="F44" s="168"/>
-      <c r="G44" s="169"/>
+      <c r="F44" s="153"/>
+      <c r="G44" s="154"/>
       <c r="H44" s="113">
         <v>4</v>
       </c>
@@ -13320,22 +13320,22 @@
       <c r="K44" s="116">
         <v>2</v>
       </c>
-      <c r="L44" s="136">
+      <c r="L44" s="124">
         <v>1</v>
       </c>
-      <c r="M44" s="136"/>
+      <c r="M44" s="124"/>
       <c r="N44" s="117" t="str">
         <f t="shared" si="4"/>
         <v>2FFF4</v>
       </c>
-      <c r="O44" s="139" t="str">
+      <c r="O44" s="141" t="str">
         <f t="shared" si="5"/>
         <v>7C 01 04 00 02 02 00 00 01 00 00 00</v>
       </c>
-      <c r="P44" s="139"/>
-      <c r="Q44" s="139"/>
-      <c r="R44" s="139"/>
-      <c r="S44" s="140"/>
+      <c r="P44" s="141"/>
+      <c r="Q44" s="141"/>
+      <c r="R44" s="141"/>
+      <c r="S44" s="142"/>
       <c r="T44" s="76"/>
       <c r="U44" s="51"/>
       <c r="V44" s="51"/>
@@ -13357,12 +13357,12 @@
       <c r="D45" s="110">
         <v>173</v>
       </c>
-      <c r="E45" s="167" t="str">
+      <c r="E45" s="152" t="str">
         <f>VLOOKUP(D45,Lookups!$D:$E,2,0)</f>
         <v>Snore</v>
       </c>
-      <c r="F45" s="168"/>
-      <c r="G45" s="169"/>
+      <c r="F45" s="153"/>
+      <c r="G45" s="154"/>
       <c r="H45" s="113">
         <v>2</v>
       </c>
@@ -13375,22 +13375,22 @@
       <c r="K45" s="116">
         <v>2</v>
       </c>
-      <c r="L45" s="136">
+      <c r="L45" s="124">
         <v>2</v>
       </c>
-      <c r="M45" s="136"/>
+      <c r="M45" s="124"/>
       <c r="N45" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30000</v>
       </c>
-      <c r="O45" s="139" t="str">
+      <c r="O45" s="141" t="str">
         <f t="shared" si="5"/>
         <v>AD 00 02 00 04 02 00 00 02 00 00 00</v>
       </c>
-      <c r="P45" s="139"/>
-      <c r="Q45" s="139"/>
-      <c r="R45" s="139"/>
-      <c r="S45" s="140"/>
+      <c r="P45" s="141"/>
+      <c r="Q45" s="141"/>
+      <c r="R45" s="141"/>
+      <c r="S45" s="142"/>
       <c r="T45" s="76"/>
       <c r="U45" s="51"/>
       <c r="V45" s="51"/>
@@ -13412,12 +13412,12 @@
       <c r="D46" s="110">
         <v>180</v>
       </c>
-      <c r="E46" s="167" t="str">
+      <c r="E46" s="152" t="str">
         <f>VLOOKUP(D46,Lookups!$D:$E,2,0)</f>
         <v>Spite</v>
       </c>
-      <c r="F46" s="168"/>
-      <c r="G46" s="169"/>
+      <c r="F46" s="153"/>
+      <c r="G46" s="154"/>
       <c r="H46" s="113">
         <v>0</v>
       </c>
@@ -13430,22 +13430,22 @@
       <c r="K46" s="116">
         <v>0</v>
       </c>
-      <c r="L46" s="136">
+      <c r="L46" s="124">
         <v>2</v>
       </c>
-      <c r="M46" s="136"/>
+      <c r="M46" s="124"/>
       <c r="N46" s="117" t="str">
         <f t="shared" si="4"/>
         <v>3000C</v>
       </c>
-      <c r="O46" s="139" t="str">
+      <c r="O46" s="141" t="str">
         <f t="shared" si="5"/>
         <v>B4 00 00 00 08 00 00 00 02 00 00 00</v>
       </c>
-      <c r="P46" s="139"/>
-      <c r="Q46" s="139"/>
-      <c r="R46" s="139"/>
-      <c r="S46" s="140"/>
+      <c r="P46" s="141"/>
+      <c r="Q46" s="141"/>
+      <c r="R46" s="141"/>
+      <c r="S46" s="142"/>
       <c r="T46" s="76"/>
       <c r="U46" s="51"/>
       <c r="V46" s="51"/>
@@ -13467,12 +13467,12 @@
       <c r="D47" s="110">
         <v>314</v>
       </c>
-      <c r="E47" s="167" t="str">
+      <c r="E47" s="152" t="str">
         <f>VLOOKUP(D47,Lookups!$D:$E,2,0)</f>
         <v>Air Cutter</v>
       </c>
-      <c r="F47" s="168"/>
-      <c r="G47" s="169"/>
+      <c r="F47" s="153"/>
+      <c r="G47" s="154"/>
       <c r="H47" s="113">
         <v>2</v>
       </c>
@@ -13485,22 +13485,22 @@
       <c r="K47" s="116">
         <v>2</v>
       </c>
-      <c r="L47" s="136">
+      <c r="L47" s="124">
         <v>0</v>
       </c>
-      <c r="M47" s="136"/>
+      <c r="M47" s="124"/>
       <c r="N47" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30018</v>
       </c>
-      <c r="O47" s="139" t="str">
+      <c r="O47" s="141" t="str">
         <f t="shared" si="5"/>
         <v>3A 01 02 04 00 02 00 00 00 00 00 00</v>
       </c>
-      <c r="P47" s="139"/>
-      <c r="Q47" s="139"/>
-      <c r="R47" s="139"/>
-      <c r="S47" s="140"/>
+      <c r="P47" s="141"/>
+      <c r="Q47" s="141"/>
+      <c r="R47" s="141"/>
+      <c r="S47" s="142"/>
       <c r="T47" s="76"/>
       <c r="U47" s="51"/>
       <c r="V47" s="51"/>
@@ -13522,12 +13522,12 @@
       <c r="D48" s="110">
         <v>270</v>
       </c>
-      <c r="E48" s="167" t="str">
+      <c r="E48" s="152" t="str">
         <f>VLOOKUP(D48,Lookups!$D:$E,2,0)</f>
         <v>Helping Hand</v>
       </c>
-      <c r="F48" s="168"/>
-      <c r="G48" s="169"/>
+      <c r="F48" s="153"/>
+      <c r="G48" s="154"/>
       <c r="H48" s="113">
         <v>2</v>
       </c>
@@ -13540,22 +13540,22 @@
       <c r="K48" s="116">
         <v>2</v>
       </c>
-      <c r="L48" s="136">
+      <c r="L48" s="124">
         <v>2</v>
       </c>
-      <c r="M48" s="136"/>
+      <c r="M48" s="124"/>
       <c r="N48" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30024</v>
       </c>
-      <c r="O48" s="139" t="str">
+      <c r="O48" s="141" t="str">
         <f t="shared" si="5"/>
         <v>0E 01 02 00 04 02 00 00 02 00 00 00</v>
       </c>
-      <c r="P48" s="139"/>
-      <c r="Q48" s="139"/>
-      <c r="R48" s="139"/>
-      <c r="S48" s="140"/>
+      <c r="P48" s="141"/>
+      <c r="Q48" s="141"/>
+      <c r="R48" s="141"/>
+      <c r="S48" s="142"/>
       <c r="T48" s="76"/>
       <c r="U48" s="51"/>
       <c r="V48" s="51"/>
@@ -13577,12 +13577,12 @@
       <c r="D49" s="110">
         <v>283</v>
       </c>
-      <c r="E49" s="167" t="str">
+      <c r="E49" s="152" t="str">
         <f>VLOOKUP(D49,Lookups!$D:$E,2,0)</f>
         <v>Endeavor</v>
       </c>
-      <c r="F49" s="168"/>
-      <c r="G49" s="169"/>
+      <c r="F49" s="153"/>
+      <c r="G49" s="154"/>
       <c r="H49" s="113">
         <v>4</v>
       </c>
@@ -13595,22 +13595,22 @@
       <c r="K49" s="116">
         <v>0</v>
       </c>
-      <c r="L49" s="136">
+      <c r="L49" s="124">
         <v>1</v>
       </c>
-      <c r="M49" s="136"/>
+      <c r="M49" s="124"/>
       <c r="N49" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30030</v>
       </c>
-      <c r="O49" s="139" t="str">
+      <c r="O49" s="141" t="str">
         <f t="shared" si="5"/>
         <v>1B 01 04 00 04 00 00 00 01 00 00 00</v>
       </c>
-      <c r="P49" s="139"/>
-      <c r="Q49" s="139"/>
-      <c r="R49" s="139"/>
-      <c r="S49" s="140"/>
+      <c r="P49" s="141"/>
+      <c r="Q49" s="141"/>
+      <c r="R49" s="141"/>
+      <c r="S49" s="142"/>
       <c r="T49" s="76"/>
       <c r="U49" s="51"/>
       <c r="V49" s="51"/>
@@ -13632,12 +13632,12 @@
       <c r="D50" s="110">
         <v>200</v>
       </c>
-      <c r="E50" s="167" t="str">
+      <c r="E50" s="152" t="str">
         <f>VLOOKUP(D50,Lookups!$D:$E,2,0)</f>
         <v>Outrage</v>
       </c>
-      <c r="F50" s="168"/>
-      <c r="G50" s="169"/>
+      <c r="F50" s="153"/>
+      <c r="G50" s="154"/>
       <c r="H50" s="113">
         <v>6</v>
       </c>
@@ -13650,22 +13650,22 @@
       <c r="K50" s="116">
         <v>0</v>
       </c>
-      <c r="L50" s="136">
+      <c r="L50" s="124">
         <v>1</v>
       </c>
-      <c r="M50" s="136"/>
+      <c r="M50" s="124"/>
       <c r="N50" s="117" t="str">
         <f t="shared" si="4"/>
         <v>3003C</v>
       </c>
-      <c r="O50" s="139" t="str">
+      <c r="O50" s="141" t="str">
         <f t="shared" si="5"/>
         <v>C8 00 06 00 02 00 00 00 01 00 00 00</v>
       </c>
-      <c r="P50" s="139"/>
-      <c r="Q50" s="139"/>
-      <c r="R50" s="139"/>
-      <c r="S50" s="140"/>
+      <c r="P50" s="141"/>
+      <c r="Q50" s="141"/>
+      <c r="R50" s="141"/>
+      <c r="S50" s="142"/>
       <c r="T50" s="76"/>
       <c r="U50" s="51"/>
       <c r="V50" s="51"/>
@@ -13687,12 +13687,12 @@
       <c r="D51" s="110">
         <v>246</v>
       </c>
-      <c r="E51" s="167" t="str">
+      <c r="E51" s="152" t="str">
         <f>VLOOKUP(D51,Lookups!$D:$E,2,0)</f>
         <v>AncientPower</v>
       </c>
-      <c r="F51" s="168"/>
-      <c r="G51" s="169"/>
+      <c r="F51" s="153"/>
+      <c r="G51" s="154"/>
       <c r="H51" s="113">
         <v>6</v>
       </c>
@@ -13705,22 +13705,22 @@
       <c r="K51" s="116">
         <v>2</v>
       </c>
-      <c r="L51" s="136">
+      <c r="L51" s="124">
         <v>1</v>
       </c>
-      <c r="M51" s="136"/>
+      <c r="M51" s="124"/>
       <c r="N51" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30048</v>
       </c>
-      <c r="O51" s="139" t="str">
+      <c r="O51" s="141" t="str">
         <f t="shared" si="5"/>
         <v>F6 00 06 00 00 02 00 00 01 00 00 00</v>
       </c>
-      <c r="P51" s="139"/>
-      <c r="Q51" s="139"/>
-      <c r="R51" s="139"/>
-      <c r="S51" s="140"/>
+      <c r="P51" s="141"/>
+      <c r="Q51" s="141"/>
+      <c r="R51" s="141"/>
+      <c r="S51" s="142"/>
       <c r="T51" s="76"/>
       <c r="U51" s="51"/>
       <c r="V51" s="51"/>
@@ -13742,12 +13742,12 @@
       <c r="D52" s="110">
         <v>235</v>
       </c>
-      <c r="E52" s="167" t="str">
+      <c r="E52" s="152" t="str">
         <f>VLOOKUP(D52,Lookups!$D:$E,2,0)</f>
         <v>Synthesis</v>
       </c>
-      <c r="F52" s="168"/>
-      <c r="G52" s="169"/>
+      <c r="F52" s="153"/>
+      <c r="G52" s="154"/>
       <c r="H52" s="113">
         <v>0</v>
       </c>
@@ -13760,22 +13760,22 @@
       <c r="K52" s="116">
         <v>6</v>
       </c>
-      <c r="L52" s="136">
+      <c r="L52" s="124">
         <v>2</v>
       </c>
-      <c r="M52" s="136"/>
+      <c r="M52" s="124"/>
       <c r="N52" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30054</v>
       </c>
-      <c r="O52" s="139" t="str">
+      <c r="O52" s="141" t="str">
         <f t="shared" si="5"/>
         <v>EB 00 00 00 02 06 00 00 02 00 00 00</v>
       </c>
-      <c r="P52" s="139"/>
-      <c r="Q52" s="139"/>
-      <c r="R52" s="139"/>
-      <c r="S52" s="140"/>
+      <c r="P52" s="141"/>
+      <c r="Q52" s="141"/>
+      <c r="R52" s="141"/>
+      <c r="S52" s="142"/>
       <c r="T52" s="76"/>
       <c r="U52" s="51"/>
       <c r="V52" s="51"/>
@@ -13797,12 +13797,12 @@
       <c r="D53" s="110">
         <v>324</v>
       </c>
-      <c r="E53" s="167" t="str">
+      <c r="E53" s="152" t="str">
         <f>VLOOKUP(D53,Lookups!$D:$E,2,0)</f>
         <v>Signal Beam</v>
       </c>
-      <c r="F53" s="168"/>
-      <c r="G53" s="169"/>
+      <c r="F53" s="153"/>
+      <c r="G53" s="154"/>
       <c r="H53" s="113">
         <v>2</v>
       </c>
@@ -13815,22 +13815,22 @@
       <c r="K53" s="116">
         <v>2</v>
       </c>
-      <c r="L53" s="136">
+      <c r="L53" s="124">
         <v>1</v>
       </c>
-      <c r="M53" s="136"/>
+      <c r="M53" s="124"/>
       <c r="N53" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30060</v>
       </c>
-      <c r="O53" s="139" t="str">
+      <c r="O53" s="141" t="str">
         <f>IF(LEN(DEC2HEX($D53))=1,"0"&amp;DEC2HEX($D53)&amp;" 00",IF(LEN(DEC2HEX($D53))=2,DEC2HEX($D53)&amp;" 00",IF(LEN(DEC2HEX($D53))=3,RIGHT(DEC2HEX($D53),2)&amp;" 0"&amp;LEFT(DEC2HEX($D53),1),IF(LEN(DEC2HEX($D53))=4,RIGHT(DEC2HEX($D53),2)&amp;" "&amp;LEFT(DEC2HEX($D53),2),"Error - Move ID too high"))))&amp;" "&amp;IF(LEN(DEC2HEX(H53))=1,"0"&amp;DEC2HEX(H53),DEC2HEX(H53))&amp;" "&amp;IF(LEN(DEC2HEX(I53))=1,"0"&amp;DEC2HEX(I53),DEC2HEX(I53))&amp;" "&amp;IF(LEN(DEC2HEX(J53))=1,"0"&amp;DEC2HEX(J53),DEC2HEX(J53))&amp;" "&amp;IF(LEN(DEC2HEX(K53))=1,"0"&amp;DEC2HEX(K53),DEC2HEX(K53))&amp;" 00 00 "&amp;IF(LEN(DEC2HEX(L53))=1,"0"&amp;DEC2HEX(L53),DEC2HEX(L53))&amp;" 00 00 00"</f>
         <v>44 01 02 02 02 02 00 00 01 00 00 00</v>
       </c>
-      <c r="P53" s="139"/>
-      <c r="Q53" s="139"/>
-      <c r="R53" s="139"/>
-      <c r="S53" s="140"/>
+      <c r="P53" s="141"/>
+      <c r="Q53" s="141"/>
+      <c r="R53" s="141"/>
+      <c r="S53" s="142"/>
       <c r="T53" s="76"/>
       <c r="U53" s="51"/>
       <c r="V53" s="51"/>
@@ -13852,12 +13852,12 @@
       <c r="D54" s="110">
         <v>428</v>
       </c>
-      <c r="E54" s="167" t="str">
+      <c r="E54" s="152" t="str">
         <f>VLOOKUP(D54,Lookups!$D:$E,2,0)</f>
         <v>Zen Headbutt</v>
       </c>
-      <c r="F54" s="168"/>
-      <c r="G54" s="169"/>
+      <c r="F54" s="153"/>
+      <c r="G54" s="154"/>
       <c r="H54" s="113">
         <v>0</v>
       </c>
@@ -13870,22 +13870,22 @@
       <c r="K54" s="116">
         <v>0</v>
       </c>
-      <c r="L54" s="136">
+      <c r="L54" s="124">
         <v>0</v>
       </c>
-      <c r="M54" s="136"/>
+      <c r="M54" s="124"/>
       <c r="N54" s="117" t="str">
         <f t="shared" si="4"/>
         <v>3006C</v>
       </c>
-      <c r="O54" s="139" t="str">
+      <c r="O54" s="141" t="str">
         <f t="shared" si="5"/>
         <v>AC 01 00 04 04 00 00 00 00 00 00 00</v>
       </c>
-      <c r="P54" s="139"/>
-      <c r="Q54" s="139"/>
-      <c r="R54" s="139"/>
-      <c r="S54" s="140"/>
+      <c r="P54" s="141"/>
+      <c r="Q54" s="141"/>
+      <c r="R54" s="141"/>
+      <c r="S54" s="142"/>
       <c r="T54" s="76"/>
       <c r="U54" s="51"/>
       <c r="V54" s="51"/>
@@ -13907,12 +13907,12 @@
       <c r="D55" s="110">
         <v>410</v>
       </c>
-      <c r="E55" s="167" t="str">
+      <c r="E55" s="152" t="str">
         <f>VLOOKUP(D55,Lookups!$D:$E,2,0)</f>
         <v>Vacuum Wave</v>
       </c>
-      <c r="F55" s="168"/>
-      <c r="G55" s="169"/>
+      <c r="F55" s="153"/>
+      <c r="G55" s="154"/>
       <c r="H55" s="113">
         <v>2</v>
       </c>
@@ -13925,22 +13925,22 @@
       <c r="K55" s="116">
         <v>2</v>
       </c>
-      <c r="L55" s="136">
+      <c r="L55" s="124">
         <v>0</v>
       </c>
-      <c r="M55" s="136"/>
+      <c r="M55" s="124"/>
       <c r="N55" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30078</v>
       </c>
-      <c r="O55" s="139" t="str">
+      <c r="O55" s="141" t="str">
         <f t="shared" si="5"/>
         <v>9A 01 02 04 00 02 00 00 00 00 00 00</v>
       </c>
-      <c r="P55" s="139"/>
-      <c r="Q55" s="139"/>
-      <c r="R55" s="139"/>
-      <c r="S55" s="140"/>
+      <c r="P55" s="141"/>
+      <c r="Q55" s="141"/>
+      <c r="R55" s="141"/>
+      <c r="S55" s="142"/>
       <c r="T55" s="76"/>
       <c r="U55" s="51"/>
       <c r="V55" s="51"/>
@@ -13962,12 +13962,12 @@
       <c r="D56" s="110">
         <v>414</v>
       </c>
-      <c r="E56" s="167" t="str">
+      <c r="E56" s="152" t="str">
         <f>VLOOKUP(D56,Lookups!$D:$E,2,0)</f>
         <v>Earth Power</v>
       </c>
-      <c r="F56" s="168"/>
-      <c r="G56" s="169"/>
+      <c r="F56" s="153"/>
+      <c r="G56" s="154"/>
       <c r="H56" s="113">
         <v>6</v>
       </c>
@@ -13980,22 +13980,22 @@
       <c r="K56" s="116">
         <v>2</v>
       </c>
-      <c r="L56" s="136">
+      <c r="L56" s="124">
         <v>1</v>
       </c>
-      <c r="M56" s="136"/>
+      <c r="M56" s="124"/>
       <c r="N56" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30084</v>
       </c>
-      <c r="O56" s="139" t="str">
+      <c r="O56" s="141" t="str">
         <f t="shared" si="5"/>
         <v>9E 01 06 00 00 02 00 00 01 00 00 00</v>
       </c>
-      <c r="P56" s="139"/>
-      <c r="Q56" s="139"/>
-      <c r="R56" s="139"/>
-      <c r="S56" s="140"/>
+      <c r="P56" s="141"/>
+      <c r="Q56" s="141"/>
+      <c r="R56" s="141"/>
+      <c r="S56" s="142"/>
       <c r="T56" s="76"/>
       <c r="U56" s="51"/>
       <c r="V56" s="51"/>
@@ -14017,12 +14017,12 @@
       <c r="D57" s="110">
         <v>441</v>
       </c>
-      <c r="E57" s="167" t="str">
+      <c r="E57" s="152" t="str">
         <f>VLOOKUP(D57,Lookups!$D:$E,2,0)</f>
         <v>Gunk Shot</v>
       </c>
-      <c r="F57" s="168"/>
-      <c r="G57" s="169"/>
+      <c r="F57" s="153"/>
+      <c r="G57" s="154"/>
       <c r="H57" s="113">
         <v>4</v>
       </c>
@@ -14035,22 +14035,22 @@
       <c r="K57" s="116">
         <v>2</v>
       </c>
-      <c r="L57" s="136">
+      <c r="L57" s="124">
         <v>1</v>
       </c>
-      <c r="M57" s="136"/>
+      <c r="M57" s="124"/>
       <c r="N57" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30090</v>
       </c>
-      <c r="O57" s="139" t="str">
+      <c r="O57" s="141" t="str">
         <f t="shared" si="5"/>
         <v>B9 01 04 02 00 02 00 00 01 00 00 00</v>
       </c>
-      <c r="P57" s="139"/>
-      <c r="Q57" s="139"/>
-      <c r="R57" s="139"/>
-      <c r="S57" s="140"/>
+      <c r="P57" s="141"/>
+      <c r="Q57" s="141"/>
+      <c r="R57" s="141"/>
+      <c r="S57" s="142"/>
       <c r="T57" s="76"/>
       <c r="U57" s="51"/>
       <c r="V57" s="51"/>
@@ -14072,12 +14072,12 @@
       <c r="D58" s="110">
         <v>239</v>
       </c>
-      <c r="E58" s="167" t="str">
+      <c r="E58" s="152" t="str">
         <f>VLOOKUP(D58,Lookups!$D:$E,2,0)</f>
         <v>Twister</v>
       </c>
-      <c r="F58" s="168"/>
-      <c r="G58" s="169"/>
+      <c r="F58" s="153"/>
+      <c r="G58" s="154"/>
       <c r="H58" s="113">
         <v>6</v>
       </c>
@@ -14090,22 +14090,22 @@
       <c r="K58" s="116">
         <v>2</v>
       </c>
-      <c r="L58" s="136">
+      <c r="L58" s="124">
         <v>1</v>
       </c>
-      <c r="M58" s="136"/>
+      <c r="M58" s="124"/>
       <c r="N58" s="117" t="str">
         <f t="shared" si="4"/>
         <v>3009C</v>
       </c>
-      <c r="O58" s="139" t="str">
+      <c r="O58" s="141" t="str">
         <f t="shared" si="5"/>
         <v>EF 00 06 00 00 02 00 00 01 00 00 00</v>
       </c>
-      <c r="P58" s="139"/>
-      <c r="Q58" s="139"/>
-      <c r="R58" s="139"/>
-      <c r="S58" s="140"/>
+      <c r="P58" s="141"/>
+      <c r="Q58" s="141"/>
+      <c r="R58" s="141"/>
+      <c r="S58" s="142"/>
       <c r="T58" s="76"/>
       <c r="U58" s="51"/>
       <c r="V58" s="51"/>
@@ -14127,12 +14127,12 @@
       <c r="D59" s="110">
         <v>402</v>
       </c>
-      <c r="E59" s="167" t="str">
+      <c r="E59" s="152" t="str">
         <f>VLOOKUP(D59,Lookups!$D:$E,2,0)</f>
         <v>Seed Bomb</v>
       </c>
-      <c r="F59" s="168"/>
-      <c r="G59" s="169"/>
+      <c r="F59" s="153"/>
+      <c r="G59" s="154"/>
       <c r="H59" s="113">
         <v>4</v>
       </c>
@@ -14145,22 +14145,22 @@
       <c r="K59" s="116">
         <v>4</v>
       </c>
-      <c r="L59" s="136">
+      <c r="L59" s="124">
         <v>1</v>
       </c>
-      <c r="M59" s="136"/>
+      <c r="M59" s="124"/>
       <c r="N59" s="117" t="str">
         <f t="shared" si="4"/>
         <v>300A8</v>
       </c>
-      <c r="O59" s="139" t="str">
+      <c r="O59" s="141" t="str">
         <f t="shared" si="5"/>
         <v>92 01 04 00 00 04 00 00 01 00 00 00</v>
       </c>
-      <c r="P59" s="139"/>
-      <c r="Q59" s="139"/>
-      <c r="R59" s="139"/>
-      <c r="S59" s="140"/>
+      <c r="P59" s="141"/>
+      <c r="Q59" s="141"/>
+      <c r="R59" s="141"/>
+      <c r="S59" s="142"/>
       <c r="T59" s="76"/>
       <c r="U59" s="51"/>
       <c r="V59" s="51"/>
@@ -14182,12 +14182,12 @@
       <c r="D60" s="110">
         <v>334</v>
       </c>
-      <c r="E60" s="167" t="str">
+      <c r="E60" s="152" t="str">
         <f>VLOOKUP(D60,Lookups!$D:$E,2,0)</f>
         <v>Iron Defense</v>
       </c>
-      <c r="F60" s="168"/>
-      <c r="G60" s="169"/>
+      <c r="F60" s="153"/>
+      <c r="G60" s="154"/>
       <c r="H60" s="113">
         <v>4</v>
       </c>
@@ -14200,22 +14200,22 @@
       <c r="K60" s="116">
         <v>0</v>
       </c>
-      <c r="L60" s="136">
+      <c r="L60" s="124">
         <v>1</v>
       </c>
-      <c r="M60" s="136"/>
+      <c r="M60" s="124"/>
       <c r="N60" s="117" t="str">
         <f t="shared" si="4"/>
         <v>300B4</v>
       </c>
-      <c r="O60" s="139" t="str">
+      <c r="O60" s="141" t="str">
         <f t="shared" si="5"/>
         <v>4E 01 04 02 02 00 00 00 01 00 00 00</v>
       </c>
-      <c r="P60" s="139"/>
-      <c r="Q60" s="139"/>
-      <c r="R60" s="139"/>
-      <c r="S60" s="140"/>
+      <c r="P60" s="141"/>
+      <c r="Q60" s="141"/>
+      <c r="R60" s="141"/>
+      <c r="S60" s="142"/>
       <c r="T60" s="76"/>
       <c r="U60" s="51"/>
       <c r="V60" s="51"/>
@@ -14237,12 +14237,12 @@
       <c r="D61" s="110">
         <v>393</v>
       </c>
-      <c r="E61" s="167" t="str">
+      <c r="E61" s="152" t="str">
         <f>VLOOKUP(D61,Lookups!$D:$E,2,0)</f>
         <v>Magnet Rise</v>
       </c>
-      <c r="F61" s="168"/>
-      <c r="G61" s="169"/>
+      <c r="F61" s="153"/>
+      <c r="G61" s="154"/>
       <c r="H61" s="113">
         <v>0</v>
       </c>
@@ -14255,22 +14255,22 @@
       <c r="K61" s="116">
         <v>2</v>
       </c>
-      <c r="L61" s="136">
+      <c r="L61" s="124">
         <v>2</v>
       </c>
-      <c r="M61" s="136"/>
+      <c r="M61" s="124"/>
       <c r="N61" s="117" t="str">
         <f t="shared" si="4"/>
         <v>300C0</v>
       </c>
-      <c r="O61" s="139" t="str">
+      <c r="O61" s="141" t="str">
         <f t="shared" si="5"/>
         <v>89 01 00 02 04 02 00 00 02 00 00 00</v>
       </c>
-      <c r="P61" s="139"/>
-      <c r="Q61" s="139"/>
-      <c r="R61" s="139"/>
-      <c r="S61" s="140"/>
+      <c r="P61" s="141"/>
+      <c r="Q61" s="141"/>
+      <c r="R61" s="141"/>
+      <c r="S61" s="142"/>
       <c r="T61" s="76"/>
       <c r="U61" s="51"/>
       <c r="V61" s="51"/>
@@ -14292,12 +14292,12 @@
       <c r="D62" s="110">
         <v>387</v>
       </c>
-      <c r="E62" s="167" t="str">
+      <c r="E62" s="152" t="str">
         <f>VLOOKUP(D62,Lookups!$D:$E,2,0)</f>
         <v>Last Resort</v>
       </c>
-      <c r="F62" s="168"/>
-      <c r="G62" s="169"/>
+      <c r="F62" s="153"/>
+      <c r="G62" s="154"/>
       <c r="H62" s="113">
         <v>0</v>
       </c>
@@ -14310,22 +14310,22 @@
       <c r="K62" s="116">
         <v>8</v>
       </c>
-      <c r="L62" s="136">
+      <c r="L62" s="124">
         <v>2</v>
       </c>
-      <c r="M62" s="136"/>
+      <c r="M62" s="124"/>
       <c r="N62" s="117" t="str">
         <f t="shared" si="4"/>
         <v>300CC</v>
       </c>
-      <c r="O62" s="139" t="str">
+      <c r="O62" s="141" t="str">
         <f t="shared" si="5"/>
         <v>83 01 00 00 00 08 00 00 02 00 00 00</v>
       </c>
-      <c r="P62" s="139"/>
-      <c r="Q62" s="139"/>
-      <c r="R62" s="139"/>
-      <c r="S62" s="140"/>
+      <c r="P62" s="141"/>
+      <c r="Q62" s="141"/>
+      <c r="R62" s="141"/>
+      <c r="S62" s="142"/>
       <c r="T62" s="76"/>
       <c r="U62" s="51"/>
       <c r="V62" s="51"/>
@@ -14347,12 +14347,12 @@
       <c r="D63" s="110">
         <v>340</v>
       </c>
-      <c r="E63" s="167" t="str">
+      <c r="E63" s="152" t="str">
         <f>VLOOKUP(D63,Lookups!$D:$E,2,0)</f>
         <v>Bounce</v>
       </c>
-      <c r="F63" s="168"/>
-      <c r="G63" s="169"/>
+      <c r="F63" s="153"/>
+      <c r="G63" s="154"/>
       <c r="H63" s="113">
         <v>4</v>
       </c>
@@ -14365,22 +14365,22 @@
       <c r="K63" s="116">
         <v>2</v>
       </c>
-      <c r="L63" s="136">
+      <c r="L63" s="124">
         <v>1</v>
       </c>
-      <c r="M63" s="136"/>
+      <c r="M63" s="124"/>
       <c r="N63" s="117" t="str">
         <f t="shared" si="4"/>
         <v>300D8</v>
       </c>
-      <c r="O63" s="139" t="str">
+      <c r="O63" s="141" t="str">
         <f t="shared" si="5"/>
         <v>54 01 04 00 02 02 00 00 01 00 00 00</v>
       </c>
-      <c r="P63" s="139"/>
-      <c r="Q63" s="139"/>
-      <c r="R63" s="139"/>
-      <c r="S63" s="140"/>
+      <c r="P63" s="141"/>
+      <c r="Q63" s="141"/>
+      <c r="R63" s="141"/>
+      <c r="S63" s="142"/>
       <c r="T63" s="76"/>
       <c r="U63" s="51"/>
       <c r="V63" s="51"/>
@@ -14402,12 +14402,12 @@
       <c r="D64" s="110">
         <v>271</v>
       </c>
-      <c r="E64" s="167" t="str">
+      <c r="E64" s="152" t="str">
         <f>VLOOKUP(D64,Lookups!$D:$E,2,0)</f>
         <v>Trick</v>
       </c>
-      <c r="F64" s="168"/>
-      <c r="G64" s="169"/>
+      <c r="F64" s="153"/>
+      <c r="G64" s="154"/>
       <c r="H64" s="113">
         <v>0</v>
       </c>
@@ -14420,22 +14420,22 @@
       <c r="K64" s="116">
         <v>0</v>
       </c>
-      <c r="L64" s="136">
+      <c r="L64" s="124">
         <v>0</v>
       </c>
-      <c r="M64" s="136"/>
+      <c r="M64" s="124"/>
       <c r="N64" s="117" t="str">
         <f t="shared" si="4"/>
         <v>300E4</v>
       </c>
-      <c r="O64" s="139" t="str">
+      <c r="O64" s="141" t="str">
         <f t="shared" si="5"/>
         <v>0F 01 00 04 04 00 00 00 00 00 00 00</v>
       </c>
-      <c r="P64" s="139"/>
-      <c r="Q64" s="139"/>
-      <c r="R64" s="139"/>
-      <c r="S64" s="140"/>
+      <c r="P64" s="141"/>
+      <c r="Q64" s="141"/>
+      <c r="R64" s="141"/>
+      <c r="S64" s="142"/>
       <c r="T64" s="76"/>
       <c r="U64" s="51"/>
       <c r="V64" s="51"/>
@@ -14457,12 +14457,12 @@
       <c r="D65" s="110">
         <v>257</v>
       </c>
-      <c r="E65" s="167" t="str">
+      <c r="E65" s="152" t="str">
         <f>VLOOKUP(D65,Lookups!$D:$E,2,0)</f>
         <v>Heat Wave</v>
       </c>
-      <c r="F65" s="168"/>
-      <c r="G65" s="169"/>
+      <c r="F65" s="153"/>
+      <c r="G65" s="154"/>
       <c r="H65" s="113">
         <v>4</v>
       </c>
@@ -14475,22 +14475,22 @@
       <c r="K65" s="116">
         <v>2</v>
       </c>
-      <c r="L65" s="136">
+      <c r="L65" s="124">
         <v>1</v>
       </c>
-      <c r="M65" s="136"/>
+      <c r="M65" s="124"/>
       <c r="N65" s="117" t="str">
         <f t="shared" si="4"/>
         <v>300F0</v>
       </c>
-      <c r="O65" s="139" t="str">
+      <c r="O65" s="141" t="str">
         <f t="shared" si="5"/>
         <v>01 01 04 02 00 02 00 00 01 00 00 00</v>
       </c>
-      <c r="P65" s="139"/>
-      <c r="Q65" s="139"/>
-      <c r="R65" s="139"/>
-      <c r="S65" s="140"/>
+      <c r="P65" s="141"/>
+      <c r="Q65" s="141"/>
+      <c r="R65" s="141"/>
+      <c r="S65" s="142"/>
       <c r="T65" s="76"/>
       <c r="U65" s="51"/>
       <c r="V65" s="51"/>
@@ -14512,12 +14512,12 @@
       <c r="D66" s="110">
         <v>282</v>
       </c>
-      <c r="E66" s="167" t="str">
+      <c r="E66" s="152" t="str">
         <f>VLOOKUP(D66,Lookups!$D:$E,2,0)</f>
         <v>Knock Off</v>
       </c>
-      <c r="F66" s="168"/>
-      <c r="G66" s="169"/>
+      <c r="F66" s="153"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="113">
         <v>4</v>
       </c>
@@ -14530,22 +14530,22 @@
       <c r="K66" s="116">
         <v>0</v>
       </c>
-      <c r="L66" s="136">
+      <c r="L66" s="124">
         <v>0</v>
       </c>
-      <c r="M66" s="136"/>
+      <c r="M66" s="124"/>
       <c r="N66" s="117" t="str">
         <f t="shared" si="4"/>
         <v>300FC</v>
       </c>
-      <c r="O66" s="139" t="str">
+      <c r="O66" s="141" t="str">
         <f t="shared" si="5"/>
         <v>1A 01 04 04 00 00 00 00 00 00 00 00</v>
       </c>
-      <c r="P66" s="139"/>
-      <c r="Q66" s="139"/>
-      <c r="R66" s="139"/>
-      <c r="S66" s="140"/>
+      <c r="P66" s="141"/>
+      <c r="Q66" s="141"/>
+      <c r="R66" s="141"/>
+      <c r="S66" s="142"/>
       <c r="T66" s="76"/>
       <c r="U66" s="51"/>
       <c r="V66" s="51"/>
@@ -14567,12 +14567,12 @@
       <c r="D67" s="110">
         <v>389</v>
       </c>
-      <c r="E67" s="167" t="str">
+      <c r="E67" s="152" t="str">
         <f>VLOOKUP(D67,Lookups!$D:$E,2,0)</f>
         <v>Sucker Punch</v>
       </c>
-      <c r="F67" s="168"/>
-      <c r="G67" s="169"/>
+      <c r="F67" s="153"/>
+      <c r="G67" s="154"/>
       <c r="H67" s="113">
         <v>0</v>
       </c>
@@ -14585,22 +14585,22 @@
       <c r="K67" s="116">
         <v>0</v>
       </c>
-      <c r="L67" s="136">
+      <c r="L67" s="124">
         <v>0</v>
       </c>
-      <c r="M67" s="136"/>
+      <c r="M67" s="124"/>
       <c r="N67" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30108</v>
       </c>
-      <c r="O67" s="139" t="str">
+      <c r="O67" s="141" t="str">
         <f t="shared" si="5"/>
         <v>85 01 00 06 02 00 00 00 00 00 00 00</v>
       </c>
-      <c r="P67" s="139"/>
-      <c r="Q67" s="139"/>
-      <c r="R67" s="139"/>
-      <c r="S67" s="140"/>
+      <c r="P67" s="141"/>
+      <c r="Q67" s="141"/>
+      <c r="R67" s="141"/>
+      <c r="S67" s="142"/>
       <c r="T67" s="76"/>
       <c r="U67" s="51"/>
       <c r="V67" s="51"/>
@@ -14622,12 +14622,12 @@
       <c r="D68" s="110">
         <v>129</v>
       </c>
-      <c r="E68" s="167" t="str">
+      <c r="E68" s="152" t="str">
         <f>VLOOKUP(D68,Lookups!$D:$E,2,0)</f>
         <v>Swift</v>
       </c>
-      <c r="F68" s="168"/>
-      <c r="G68" s="169"/>
+      <c r="F68" s="153"/>
+      <c r="G68" s="154"/>
       <c r="H68" s="113">
         <v>0</v>
       </c>
@@ -14640,22 +14640,22 @@
       <c r="K68" s="116">
         <v>4</v>
       </c>
-      <c r="L68" s="136">
+      <c r="L68" s="124">
         <v>2</v>
       </c>
-      <c r="M68" s="136"/>
+      <c r="M68" s="124"/>
       <c r="N68" s="117" t="str">
         <f t="shared" si="4"/>
         <v>30114</v>
       </c>
-      <c r="O68" s="139" t="str">
+      <c r="O68" s="141" t="str">
         <f t="shared" si="5"/>
         <v>81 00 00 02 02 04 00 00 02 00 00 00</v>
       </c>
-      <c r="P68" s="139"/>
-      <c r="Q68" s="139"/>
-      <c r="R68" s="139"/>
-      <c r="S68" s="140"/>
+      <c r="P68" s="141"/>
+      <c r="Q68" s="141"/>
+      <c r="R68" s="141"/>
+      <c r="S68" s="142"/>
       <c r="T68" s="76"/>
       <c r="U68" s="51"/>
       <c r="V68" s="51"/>
@@ -14695,22 +14695,22 @@
       <c r="K69" s="121">
         <v>2</v>
       </c>
-      <c r="L69" s="137">
+      <c r="L69" s="145">
         <v>2</v>
       </c>
-      <c r="M69" s="137"/>
+      <c r="M69" s="145"/>
       <c r="N69" s="122" t="str">
         <f t="shared" si="4"/>
         <v>30120</v>
       </c>
-      <c r="O69" s="141" t="str">
+      <c r="O69" s="143" t="str">
         <f t="shared" si="5"/>
         <v>FD 00 00 00 06 02 00 00 02 00 00 00</v>
       </c>
-      <c r="P69" s="141"/>
-      <c r="Q69" s="141"/>
-      <c r="R69" s="141"/>
-      <c r="S69" s="142"/>
+      <c r="P69" s="143"/>
+      <c r="Q69" s="143"/>
+      <c r="R69" s="143"/>
+      <c r="S69" s="144"/>
       <c r="T69" s="76"/>
       <c r="U69" s="51"/>
       <c r="V69" s="51"/>
@@ -14758,18 +14758,18 @@
     <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="51"/>
       <c r="B71" s="62"/>
-      <c r="C71" s="125" t="s">
+      <c r="C71" s="148" t="s">
         <v>992</v>
       </c>
-      <c r="D71" s="125"/>
-      <c r="E71" s="125"/>
-      <c r="F71" s="125"/>
-      <c r="G71" s="125"/>
-      <c r="H71" s="125"/>
-      <c r="I71" s="125"/>
-      <c r="J71" s="125"/>
-      <c r="K71" s="125"/>
-      <c r="L71" s="125"/>
+      <c r="D71" s="148"/>
+      <c r="E71" s="148"/>
+      <c r="F71" s="148"/>
+      <c r="G71" s="148"/>
+      <c r="H71" s="148"/>
+      <c r="I71" s="148"/>
+      <c r="J71" s="148"/>
+      <c r="K71" s="148"/>
+      <c r="L71" s="148"/>
       <c r="M71" s="24"/>
       <c r="N71" s="81" t="s">
         <v>1</v>
@@ -14794,16 +14794,16 @@
     <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="51"/>
       <c r="B72" s="62"/>
-      <c r="C72" s="125"/>
-      <c r="D72" s="125"/>
-      <c r="E72" s="125"/>
-      <c r="F72" s="125"/>
-      <c r="G72" s="125"/>
-      <c r="H72" s="125"/>
-      <c r="I72" s="125"/>
-      <c r="J72" s="125"/>
-      <c r="K72" s="125"/>
-      <c r="L72" s="125"/>
+      <c r="C72" s="148"/>
+      <c r="D72" s="148"/>
+      <c r="E72" s="148"/>
+      <c r="F72" s="148"/>
+      <c r="G72" s="148"/>
+      <c r="H72" s="148"/>
+      <c r="I72" s="148"/>
+      <c r="J72" s="148"/>
+      <c r="K72" s="148"/>
+      <c r="L72" s="148"/>
       <c r="M72" s="24"/>
       <c r="N72" s="117" t="str">
         <f>N32</f>
@@ -14895,26 +14895,26 @@
     <row r="75" spans="1:30" ht="159" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="51"/>
       <c r="B75" s="62"/>
-      <c r="C75" s="123" t="str">
+      <c r="C75" s="146" t="str">
         <f>O32&amp;" "&amp;O33&amp;" "&amp;O34&amp;" "&amp;O35&amp;" "&amp;O36&amp;" "&amp;O37&amp;" "&amp;O38&amp;" "&amp;O39&amp;" "&amp;O40&amp;" "&amp;O41&amp;" "&amp;O42&amp;" "&amp;O43&amp;" "&amp;O44&amp;" "&amp;O45&amp;" "&amp;O46&amp;" "&amp;O47&amp;" "&amp;O48&amp;" "&amp;O49&amp;" "&amp;O50&amp;" "&amp;O51&amp;" "&amp;O52&amp;" "&amp;O53&amp;" "&amp;O54&amp;" "&amp;O55&amp;" "&amp;O56&amp;" "&amp;O57&amp;" "&amp;O58&amp;" "&amp;O59&amp;" "&amp;O60&amp;" "&amp;O61&amp;" "&amp;O62&amp;" "&amp;O63&amp;" "&amp;O64&amp;" "&amp;O65&amp;" "&amp;O66&amp;" "&amp;O67&amp;" "&amp;O68&amp;" "&amp;O69</f>
         <v>23 01 02 04 02 00 00 00 00 00 00 00 BD 00 04 04 00 00 00 00 01 00 00 00 D2 00 00 08 00 00 00 00 00 00 00 00 C4 00 00 06 00 02 00 00 00 00 00 00 CD 00 04 02 00 02 00 00 01 00 00 00 09 00 02 06 00 00 00 00 00 00 00 00 07 00 02 06 00 00 00 00 00 00 00 00 14 01 08 00 00 00 00 00 01 00 00 00 08 00 02 06 00 00 00 00 00 00 00 00 BA 01 06 00 02 00 00 00 01 00 00 00 91 01 06 00 00 02 00 00 01 00 00 00 D2 01 00 06 00 02 00 00 00 00 00 00 7C 01 04 00 02 02 00 00 01 00 00 00 AD 00 02 00 04 02 00 00 02 00 00 00 B4 00 00 00 08 00 00 00 02 00 00 00 3A 01 02 04 00 02 00 00 00 00 00 00 0E 01 02 00 04 02 00 00 02 00 00 00 1B 01 04 00 04 00 00 00 01 00 00 00 C8 00 06 00 02 00 00 00 01 00 00 00 F6 00 06 00 00 02 00 00 01 00 00 00 EB 00 00 00 02 06 00 00 02 00 00 00 44 01 02 02 02 02 00 00 01 00 00 00 AC 01 00 04 04 00 00 00 00 00 00 00 9A 01 02 04 00 02 00 00 00 00 00 00 9E 01 06 00 00 02 00 00 01 00 00 00 B9 01 04 02 00 02 00 00 01 00 00 00 EF 00 06 00 00 02 00 00 01 00 00 00 92 01 04 00 00 04 00 00 01 00 00 00 4E 01 04 02 02 00 00 00 01 00 00 00 89 01 00 02 04 02 00 00 02 00 00 00 83 01 00 00 00 08 00 00 02 00 00 00 54 01 04 00 02 02 00 00 01 00 00 00 0F 01 00 04 04 00 00 00 00 00 00 00 01 01 04 02 00 02 00 00 01 00 00 00 1A 01 04 04 00 00 00 00 00 00 00 00 85 01 00 06 02 00 00 00 00 00 00 00 81 00 00 02 02 04 00 00 02 00 00 00 FD 00 00 00 06 02 00 00 02 00 00 00</v>
       </c>
-      <c r="D75" s="123"/>
-      <c r="E75" s="123"/>
-      <c r="F75" s="123"/>
-      <c r="G75" s="123"/>
-      <c r="H75" s="123"/>
-      <c r="I75" s="123"/>
-      <c r="J75" s="123"/>
-      <c r="K75" s="123"/>
-      <c r="L75" s="123"/>
-      <c r="M75" s="123"/>
-      <c r="N75" s="123"/>
-      <c r="O75" s="123"/>
-      <c r="P75" s="123"/>
-      <c r="Q75" s="123"/>
-      <c r="R75" s="123"/>
-      <c r="S75" s="123"/>
+      <c r="D75" s="146"/>
+      <c r="E75" s="146"/>
+      <c r="F75" s="146"/>
+      <c r="G75" s="146"/>
+      <c r="H75" s="146"/>
+      <c r="I75" s="146"/>
+      <c r="J75" s="146"/>
+      <c r="K75" s="146"/>
+      <c r="L75" s="146"/>
+      <c r="M75" s="146"/>
+      <c r="N75" s="146"/>
+      <c r="O75" s="146"/>
+      <c r="P75" s="146"/>
+      <c r="Q75" s="146"/>
+      <c r="R75" s="146"/>
+      <c r="S75" s="146"/>
       <c r="T75" s="76"/>
       <c r="U75" s="51"/>
       <c r="V75" s="51"/>
@@ -14990,6 +14990,129 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="dFRp7SbgY4kzXvX2NxWtx//ij6O7zbedi2vPHZGrJSCvJstwZnE+ULW6ULLMv5VTD6WQbfok6jhMQbBvAN0Hbg==" saltValue="T/zzRERB2vBl/CAfvMSM2A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="147">
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="C71:L72"/>
+    <mergeCell ref="C74:S74"/>
+    <mergeCell ref="C75:S75"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="O68:S68"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="O69:S69"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="O66:S66"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="O67:S67"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="O64:S64"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="O65:S65"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="O62:S62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="O63:S63"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="O60:S60"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="O61:S61"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="O58:S58"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="O59:S59"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="O56:S56"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="O57:S57"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="O54:S54"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="O55:S55"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="O52:S52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="O53:S53"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="O50:S50"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="O51:S51"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="O48:S48"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="O49:S49"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="O46:S46"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="O47:S47"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="O44:S44"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="O45:S45"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="O31:S31"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="O42:S42"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="O43:S43"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="O40:S40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="O41:S41"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="O38:S38"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="O39:S39"/>
     <mergeCell ref="E31:G31"/>
     <mergeCell ref="E32:G32"/>
     <mergeCell ref="L36:M36"/>
@@ -15014,129 +15137,6 @@
     <mergeCell ref="B27:K28"/>
     <mergeCell ref="L27:L28"/>
     <mergeCell ref="M27:T28"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="O31:S31"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="O42:S42"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="O43:S43"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="O40:S40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="O41:S41"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="O38:S38"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="O39:S39"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="O48:S48"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="O49:S49"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="O46:S46"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="O47:S47"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="O44:S44"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="O45:S45"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="O54:S54"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="O55:S55"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="O52:S52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="O53:S53"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="O50:S50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="O51:S51"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="O60:S60"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="O61:S61"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="O58:S58"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="O59:S59"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="O56:S56"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="O57:S57"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="O67:S67"/>
-    <mergeCell ref="E66:G66"/>
-    <mergeCell ref="E67:G67"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="O64:S64"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="O65:S65"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="O62:S62"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="O63:S63"/>
-    <mergeCell ref="C71:L72"/>
-    <mergeCell ref="C74:S74"/>
-    <mergeCell ref="C75:S75"/>
-    <mergeCell ref="E65:G65"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="E52:G52"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="E60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="O68:S68"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="O69:S69"/>
-    <mergeCell ref="E68:G68"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="O66:S66"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H9:J9"/>
   </mergeCells>
   <conditionalFormatting sqref="R26 N26 H26:J26 D26 D78:D1048576 H78:J1048576 N78:N1048576 R78:R1048576">
     <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
@@ -15217,7 +15217,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="O6 K6 C75 N32:S69 N72" unlockedFormula="1"/>
+    <ignoredError sqref="O6 C75 N32:S69 N72" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
